--- a/data/payments_incident_sample.xlsx
+++ b/data/payments_incident_sample.xlsx
@@ -8,26 +8,29 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\udita\Documents\Udit Files\code\WU\Dashboard for executive view\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15CE5D84-DEB8-4D4D-B8B1-055C240DAAA8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C81BF62-8B5B-44C2-A456-B34E3BE3CF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
-    <sheet name="APN_VOLUME" sheetId="2" r:id="rId2"/>
-    <sheet name="SUGGESTIONS" sheetId="3" r:id="rId3"/>
-    <sheet name="REROUTE" sheetId="4" r:id="rId4"/>
-    <sheet name="CONFIG" sheetId="5" r:id="rId5"/>
+    <sheet name="Sheet1" sheetId="6" r:id="rId2"/>
+    <sheet name="APN_VOLUME" sheetId="2" r:id="rId3"/>
+    <sheet name="SUGGESTIONS" sheetId="3" r:id="rId4"/>
+    <sheet name="REROUTE" sheetId="4" r:id="rId5"/>
+    <sheet name="CONFIG" sheetId="5" r:id="rId6"/>
+    <sheet name="RejectionData" sheetId="7" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">DATA!$A$1:$AJ$201</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">RejectionData!$A$1:$U$3</definedName>
   </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7249" uniqueCount="1637">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7310" uniqueCount="1690">
   <si>
     <t>Incident</t>
   </si>
@@ -4938,19 +4941,190 @@
   </si>
   <si>
     <t>Inprogress</t>
+  </si>
+  <si>
+    <t>PAYOUTID</t>
+  </si>
+  <si>
+    <t>CORRELATIONID</t>
+  </si>
+  <si>
+    <t>MTCN</t>
+  </si>
+  <si>
+    <t>CREATEDON</t>
+  </si>
+  <si>
+    <t>LASTUPDATED</t>
+  </si>
+  <si>
+    <t>MONTH</t>
+  </si>
+  <si>
+    <t>STATUS</t>
+  </si>
+  <si>
+    <t>DESCRIPTION</t>
+  </si>
+  <si>
+    <t>PARTNER_REJECTREASON</t>
+  </si>
+  <si>
+    <t>APN_REJECTREASON</t>
+  </si>
+  <si>
+    <t>SUBSTATE</t>
+  </si>
+  <si>
+    <t>PARTNERNAME</t>
+  </si>
+  <si>
+    <t>SENDCOUNTRYCODE</t>
+  </si>
+  <si>
+    <t>PURPOSE</t>
+  </si>
+  <si>
+    <t>CHANNEL</t>
+  </si>
+  <si>
+    <t>SENDINGCHANNEL</t>
+  </si>
+  <si>
+    <t>BANKNAME</t>
+  </si>
+  <si>
+    <t>BANKCODE</t>
+  </si>
+  <si>
+    <t>DELIVERYSERVICE</t>
+  </si>
+  <si>
+    <t>6119540831</t>
+  </si>
+  <si>
+    <t>2634463998825047</t>
+  </si>
+  <si>
+    <t>29/1/2026 04:47</t>
+  </si>
+  <si>
+    <t>29/1/2026 06:31</t>
+  </si>
+  <si>
+    <t>29-Jan-26</t>
+  </si>
+  <si>
+    <t>78|78</t>
+  </si>
+  <si>
+    <t>Compliance Hold</t>
+  </si>
+  <si>
+    <t>INVALID_BENEFICIARY</t>
+  </si>
+  <si>
+    <t>null</t>
+  </si>
+  <si>
+    <t>REJECTED</t>
+  </si>
+  <si>
+    <t>VISA</t>
+  </si>
+  <si>
+    <t>IN</t>
+  </si>
+  <si>
+    <t>FAMILY_SUPPORT</t>
+  </si>
+  <si>
+    <t>MOBILE</t>
+  </si>
+  <si>
+    <t>ONLINE</t>
+  </si>
+  <si>
+    <t>BANK OF AMERICA</t>
+  </si>
+  <si>
+    <t>BOFA</t>
+  </si>
+  <si>
+    <t>CASH_PICKUP</t>
+  </si>
+  <si>
+    <t>6585126461</t>
+  </si>
+  <si>
+    <t>2631024350602916</t>
+  </si>
+  <si>
+    <t>27/2/2026 18:17</t>
+  </si>
+  <si>
+    <t>27/2/2026 18:23</t>
+  </si>
+  <si>
+    <t>27-Feb-26</t>
+  </si>
+  <si>
+    <t>90|90</t>
+  </si>
+  <si>
+    <t>Beneficiary Name Mismatch</t>
+  </si>
+  <si>
+    <t>LIMIT_EXCEEDED</t>
+  </si>
+  <si>
+    <t>VALIDATION_FAILED</t>
+  </si>
+  <si>
+    <t>US</t>
+  </si>
+  <si>
+    <t>EDUCATION</t>
+  </si>
+  <si>
+    <t>WEBMDC</t>
+  </si>
+  <si>
+    <t>AGENT</t>
+  </si>
+  <si>
+    <t>STATE BANK OF INDIA</t>
+  </si>
+  <si>
+    <t>SBIN</t>
+  </si>
+  <si>
+    <t>RETURNED</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="1" x14ac:knownFonts="1">
+  <fonts count="3" x14ac:knownFonts="1">
     <font>
       <sz val="12"/>
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <name val="Calibri"/>
     </font>
   </fonts>
   <fills count="2">
@@ -4961,7 +5135,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="1">
+  <borders count="2">
     <border>
       <left/>
       <right/>
@@ -4969,15 +5143,36 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="2">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
+    <cellStyle name="Normal 2" xfId="1" xr:uid="{5A609A5E-01E4-43B8-BD5D-008BB95A05A4}"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleMedium4"/>
@@ -5316,9 +5511,9 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr filterMode="1"/>
   <dimension ref="A1:AJ201"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -5428,7 +5623,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="2" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>178</v>
       </c>
@@ -5538,7 +5733,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="3" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>338</v>
       </c>
@@ -5648,7 +5843,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="4" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>416</v>
       </c>
@@ -5758,7 +5953,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="5" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>439</v>
       </c>
@@ -5868,7 +6063,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="6" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>693</v>
       </c>
@@ -5978,7 +6173,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="7" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>825</v>
       </c>
@@ -6088,7 +6283,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="8" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>875</v>
       </c>
@@ -6198,7 +6393,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="9" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>1009</v>
       </c>
@@ -6308,7 +6503,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="10" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>1016</v>
       </c>
@@ -6418,7 +6613,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="11" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>1059</v>
       </c>
@@ -6528,7 +6723,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="12" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>1333</v>
       </c>
@@ -6638,7 +6833,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="13" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>1371</v>
       </c>
@@ -6748,7 +6943,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="14" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>1414</v>
       </c>
@@ -6858,7 +7053,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="15" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A15" t="s">
         <v>1434</v>
       </c>
@@ -6968,7 +7163,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="16" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>1474</v>
       </c>
@@ -7078,7 +7273,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="17" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>1559</v>
       </c>
@@ -7188,7 +7383,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="18" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>1565</v>
       </c>
@@ -7298,7 +7493,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="19" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A19" t="s">
         <v>1296</v>
       </c>
@@ -7405,7 +7600,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="20" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>1392</v>
       </c>
@@ -7512,7 +7707,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="21" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>1426</v>
       </c>
@@ -7622,7 +7817,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="22" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>1593</v>
       </c>
@@ -7729,7 +7924,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="23" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A23" t="s">
         <v>1288</v>
       </c>
@@ -7839,7 +8034,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="24" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>122</v>
       </c>
@@ -7949,7 +8144,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="25" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>187</v>
       </c>
@@ -8059,7 +8254,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="26" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>203</v>
       </c>
@@ -8169,7 +8364,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="27" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>211</v>
       </c>
@@ -8279,7 +8474,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>267</v>
       </c>
@@ -8389,7 +8584,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="29" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>346</v>
       </c>
@@ -8499,7 +8694,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="30" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>462</v>
       </c>
@@ -8606,7 +8801,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="31" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>524</v>
       </c>
@@ -8716,7 +8911,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="32" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>584</v>
       </c>
@@ -8826,7 +9021,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="33" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>715</v>
       </c>
@@ -8936,7 +9131,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="34" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>860</v>
       </c>
@@ -9043,7 +9238,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="35" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>883</v>
       </c>
@@ -9153,7 +9348,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="36" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>913</v>
       </c>
@@ -9263,7 +9458,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="37" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>928</v>
       </c>
@@ -9373,7 +9568,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="38" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>951</v>
       </c>
@@ -9483,7 +9678,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="39" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>974</v>
       </c>
@@ -9593,7 +9788,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="40" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>1081</v>
       </c>
@@ -9700,7 +9895,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="41" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>1089</v>
       </c>
@@ -9810,7 +10005,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="42" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>1185</v>
       </c>
@@ -9917,7 +10112,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="43" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>1229</v>
       </c>
@@ -10027,7 +10222,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="44" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>1318</v>
       </c>
@@ -10137,7 +10332,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="45" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>1406</v>
       </c>
@@ -10247,7 +10442,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="46" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>1468</v>
       </c>
@@ -10354,7 +10549,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="47" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>1516</v>
       </c>
@@ -10464,7 +10659,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="48" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>1538</v>
       </c>
@@ -10574,7 +10769,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="49" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>1572</v>
       </c>
@@ -10684,7 +10879,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="50" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>1579</v>
       </c>
@@ -10794,7 +10989,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="51" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>1214</v>
       </c>
@@ -10901,7 +11096,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="52" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>90</v>
       </c>
@@ -11011,7 +11206,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="53" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>104</v>
       </c>
@@ -11121,7 +11316,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="54" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>195</v>
       </c>
@@ -11231,7 +11426,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="55" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>244</v>
       </c>
@@ -11341,7 +11536,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="56" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>252</v>
       </c>
@@ -11451,7 +11646,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="57" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>260</v>
       </c>
@@ -11561,7 +11756,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="58" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>275</v>
       </c>
@@ -11671,7 +11866,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="59" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>292</v>
       </c>
@@ -11781,7 +11976,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="60" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>307</v>
       </c>
@@ -11891,7 +12086,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="61" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>315</v>
       </c>
@@ -12001,7 +12196,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="62" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>377</v>
       </c>
@@ -12111,7 +12306,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="63" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="63" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A63" t="s">
         <v>423</v>
       </c>
@@ -12221,7 +12416,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="64" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>454</v>
       </c>
@@ -12331,7 +12526,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="65" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="65" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A65" t="s">
         <v>494</v>
       </c>
@@ -12441,7 +12636,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="66" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>608</v>
       </c>
@@ -12551,7 +12746,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="67" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>639</v>
       </c>
@@ -12661,7 +12856,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="68" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>723</v>
       </c>
@@ -12771,7 +12966,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="69" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>786</v>
       </c>
@@ -12881,7 +13076,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="70" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>838</v>
       </c>
@@ -12988,7 +13183,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="71" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>868</v>
       </c>
@@ -13098,7 +13293,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="72" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>906</v>
       </c>
@@ -13208,7 +13403,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="73" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>920</v>
       </c>
@@ -13318,7 +13513,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="74" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>1032</v>
       </c>
@@ -13425,7 +13620,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="75" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>1113</v>
       </c>
@@ -13535,7 +13730,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="76" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="76" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A76" t="s">
         <v>1120</v>
       </c>
@@ -13645,7 +13840,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="77" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>1149</v>
       </c>
@@ -13752,7 +13947,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="78" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>1155</v>
       </c>
@@ -13862,7 +14057,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="79" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>1207</v>
       </c>
@@ -13972,7 +14167,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="80" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>1252</v>
       </c>
@@ -14082,7 +14277,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="81" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>1304</v>
       </c>
@@ -14189,7 +14384,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="82" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="82" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A82" t="s">
         <v>1311</v>
       </c>
@@ -14299,7 +14494,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="83" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="83" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A83" t="s">
         <v>1363</v>
       </c>
@@ -14409,7 +14604,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="84" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>1397</v>
       </c>
@@ -14519,7 +14714,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="85" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>1419</v>
       </c>
@@ -14626,7 +14821,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="86" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>1454</v>
       </c>
@@ -14736,7 +14931,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="87" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>1461</v>
       </c>
@@ -14846,7 +15041,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="88" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="88" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A88" t="s">
         <v>1532</v>
       </c>
@@ -14953,7 +15148,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="89" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="89" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A89" t="s">
         <v>159</v>
       </c>
@@ -15063,7 +15258,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="90" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="90" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A90" t="s">
         <v>227</v>
       </c>
@@ -15173,7 +15368,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="91" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>284</v>
       </c>
@@ -15283,7 +15478,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="92" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>400</v>
       </c>
@@ -15393,7 +15588,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="93" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>517</v>
       </c>
@@ -15503,7 +15698,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="94" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>560</v>
       </c>
@@ -15613,7 +15808,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="95" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>616</v>
       </c>
@@ -15723,7 +15918,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="96" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>655</v>
       </c>
@@ -15833,7 +16028,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="97" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>746</v>
       </c>
@@ -15943,7 +16138,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="98" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>817</v>
       </c>
@@ -16053,7 +16248,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="99" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>852</v>
       </c>
@@ -16163,7 +16358,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="100" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>959</v>
       </c>
@@ -16273,7 +16468,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="101" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>1003</v>
       </c>
@@ -16383,7 +16578,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="102" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>1128</v>
       </c>
@@ -16493,7 +16688,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="103" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>1135</v>
       </c>
@@ -16603,7 +16798,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="104" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>1273</v>
       </c>
@@ -16713,7 +16908,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="105" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>1326</v>
       </c>
@@ -16823,7 +17018,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="106" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>1493</v>
       </c>
@@ -16933,7 +17128,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="107" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>1500</v>
       </c>
@@ -17043,7 +17238,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="108" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>1545</v>
       </c>
@@ -17153,7 +17348,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="109" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>169</v>
       </c>
@@ -17260,7 +17455,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="110" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>323</v>
       </c>
@@ -17370,7 +17565,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="111" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>331</v>
       </c>
@@ -17480,7 +17675,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="112" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>362</v>
       </c>
@@ -17590,7 +17785,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="113" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>369</v>
       </c>
@@ -17700,7 +17895,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="114" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>407</v>
       </c>
@@ -17810,7 +18005,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="115" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>532</v>
       </c>
@@ -17917,7 +18112,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="116" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>546</v>
       </c>
@@ -18027,7 +18222,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="117" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>568</v>
       </c>
@@ -18137,7 +18332,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="118" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>601</v>
       </c>
@@ -18247,7 +18442,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="119" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>647</v>
       </c>
@@ -18354,7 +18549,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="120" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>730</v>
       </c>
@@ -18464,7 +18659,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="121" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>738</v>
       </c>
@@ -18574,7 +18769,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="122" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>801</v>
       </c>
@@ -18681,7 +18876,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="123" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>832</v>
       </c>
@@ -18788,7 +18983,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="124" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>1039</v>
       </c>
@@ -18895,7 +19090,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="125" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>36</v>
       </c>
@@ -19005,7 +19200,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="126" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>143</v>
       </c>
@@ -19115,7 +19310,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="127" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>447</v>
       </c>
@@ -19225,7 +19420,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="128" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>470</v>
       </c>
@@ -19335,7 +19530,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="129" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>553</v>
       </c>
@@ -19445,7 +19640,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="130" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>663</v>
       </c>
@@ -19555,7 +19750,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="131" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>685</v>
       </c>
@@ -19665,7 +19860,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="132" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>891</v>
       </c>
@@ -19775,7 +19970,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="133" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>935</v>
       </c>
@@ -19885,7 +20080,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="134" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>943</v>
       </c>
@@ -19995,7 +20190,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="135" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>967</v>
       </c>
@@ -20105,7 +20300,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="136" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>987</v>
       </c>
@@ -20215,7 +20410,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="137" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>995</v>
       </c>
@@ -20325,7 +20520,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="138" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>1024</v>
       </c>
@@ -20435,7 +20630,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="139" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>1053</v>
       </c>
@@ -20545,7 +20740,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="140" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>1066</v>
       </c>
@@ -20655,7 +20850,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="141" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>1073</v>
       </c>
@@ -20765,7 +20960,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="142" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>1192</v>
       </c>
@@ -20875,7 +21070,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="143" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>1236</v>
       </c>
@@ -20985,7 +21180,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="144" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>1259</v>
       </c>
@@ -21095,7 +21290,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="145" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>1349</v>
       </c>
@@ -21205,7 +21400,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="146" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="146" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A146" t="s">
         <v>1441</v>
       </c>
@@ -21315,7 +21510,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="147" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>1448</v>
       </c>
@@ -21425,7 +21620,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="148" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>72</v>
       </c>
@@ -21532,7 +21727,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="149" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>236</v>
       </c>
@@ -21642,7 +21837,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="150" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>299</v>
       </c>
@@ -21752,7 +21947,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="151" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>385</v>
       </c>
@@ -21862,7 +22057,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="152" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>392</v>
       </c>
@@ -21972,7 +22167,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="153" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>502</v>
       </c>
@@ -22079,7 +22274,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="154" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>510</v>
       </c>
@@ -22189,7 +22384,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="155" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>539</v>
       </c>
@@ -22296,7 +22491,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="156" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>701</v>
       </c>
@@ -22406,7 +22601,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="157" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>762</v>
       </c>
@@ -22516,7 +22711,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="158" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>770</v>
       </c>
@@ -22626,7 +22821,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="159" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>980</v>
       </c>
@@ -22736,7 +22931,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="160" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>1046</v>
       </c>
@@ -22846,7 +23041,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="161" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>1095</v>
       </c>
@@ -22956,7 +23151,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="162" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>1142</v>
       </c>
@@ -23066,7 +23261,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="163" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>1266</v>
       </c>
@@ -23176,7 +23371,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="164" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>1281</v>
       </c>
@@ -23283,7 +23478,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="165" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>1341</v>
       </c>
@@ -23393,7 +23588,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="166" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>1356</v>
       </c>
@@ -23503,7 +23698,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="167" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>1378</v>
       </c>
@@ -23613,7 +23808,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="168" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>1480</v>
       </c>
@@ -23723,7 +23918,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="169" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="169" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A169" t="s">
         <v>1487</v>
       </c>
@@ -23833,7 +24028,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="170" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>1508</v>
       </c>
@@ -23943,7 +24138,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="171" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>1524</v>
       </c>
@@ -24053,7 +24248,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="172" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>1552</v>
       </c>
@@ -24160,7 +24355,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="173" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>132</v>
       </c>
@@ -24270,7 +24465,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="174" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="174" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A174" t="s">
         <v>150</v>
       </c>
@@ -24380,7 +24575,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="175" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="175" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A175" t="s">
         <v>219</v>
       </c>
@@ -24490,7 +24685,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="176" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="176" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A176" t="s">
         <v>355</v>
       </c>
@@ -24600,7 +24795,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="177" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="177" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A177" t="s">
         <v>431</v>
       </c>
@@ -24710,7 +24905,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="178" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="178" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A178" t="s">
         <v>478</v>
       </c>
@@ -24820,7 +25015,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="179" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>486</v>
       </c>
@@ -24930,7 +25125,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="180" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>576</v>
       </c>
@@ -25040,7 +25235,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="181" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>592</v>
       </c>
@@ -25150,7 +25345,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="182" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>624</v>
       </c>
@@ -25260,7 +25455,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="183" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>632</v>
       </c>
@@ -25370,7 +25565,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="184" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>670</v>
       </c>
@@ -25477,7 +25672,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="185" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>677</v>
       </c>
@@ -25584,7 +25779,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="186" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>708</v>
       </c>
@@ -25694,7 +25889,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="187" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>754</v>
       </c>
@@ -25804,7 +25999,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="188" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>778</v>
       </c>
@@ -25914,7 +26109,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="189" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>793</v>
       </c>
@@ -26024,7 +26219,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="190" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>809</v>
       </c>
@@ -26134,7 +26329,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="191" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>845</v>
       </c>
@@ -26244,7 +26439,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="192" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>898</v>
       </c>
@@ -26354,7 +26549,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="193" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>1162</v>
       </c>
@@ -26464,7 +26659,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="194" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="194" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A194" t="s">
         <v>1169</v>
       </c>
@@ -26574,7 +26769,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="195" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>1177</v>
       </c>
@@ -26684,7 +26879,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="196" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>1199</v>
       </c>
@@ -26794,7 +26989,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="197" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>1222</v>
       </c>
@@ -26904,7 +27099,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="198" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>1385</v>
       </c>
@@ -27014,7 +27209,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="199" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>1586</v>
       </c>
@@ -27124,7 +27319,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="200" spans="1:36" ht="15.6" hidden="1" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:36" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>1244</v>
       </c>
@@ -27234,7 +27429,7 @@
         <v>1103</v>
       </c>
     </row>
-    <row r="201" spans="1:36" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:36" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>1104</v>
       </c>
@@ -27360,11 +27555,20 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B07FD6A5-EEFC-4886-8186-A1A2F0493741}">
+  <dimension ref="A1"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetData/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:F3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1600</v>
       </c>
@@ -27384,7 +27588,7 @@
         <v>1605</v>
       </c>
     </row>
-    <row r="2" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>375</v>
       </c>
@@ -27404,7 +27608,7 @@
         <v>1607</v>
       </c>
     </row>
-    <row r="3" spans="1:6" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1608</v>
       </c>
@@ -27432,12 +27636,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1612</v>
       </c>
@@ -27445,7 +27649,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>101</v>
       </c>
@@ -27453,7 +27657,7 @@
         <v>1614</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>37</v>
       </c>
@@ -27469,12 +27673,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
   <dimension ref="A1:B4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1616</v>
       </c>
@@ -27482,7 +27686,7 @@
         <v>1617</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1618</v>
       </c>
@@ -27490,7 +27694,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1620</v>
       </c>
@@ -27498,7 +27702,7 @@
         <v>1621</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1622</v>
       </c>
@@ -27514,12 +27718,12 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
   <dimension ref="A1:B5"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>1624</v>
       </c>
@@ -27527,7 +27731,7 @@
         <v>1625</v>
       </c>
     </row>
-    <row r="2" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>1626</v>
       </c>
@@ -27535,7 +27739,7 @@
         <v>1627</v>
       </c>
     </row>
-    <row r="3" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>1628</v>
       </c>
@@ -27543,7 +27747,7 @@
         <v>1629</v>
       </c>
     </row>
-    <row r="4" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>1630</v>
       </c>
@@ -27551,7 +27755,7 @@
         <v>1631</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="15.6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>1632</v>
       </c>
@@ -27565,4 +27769,210 @@
     <ignoredError sqref="A1:B5" numberStoredAsText="1"/>
   </ignoredErrors>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB98BCD-633E-4EC9-B3A3-92667D1A84E5}">
+  <dimension ref="A1:U3"/>
+  <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
+  <sheetData>
+    <row r="1" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>1637</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1638</v>
+      </c>
+      <c r="C1" s="2" t="s">
+        <v>1639</v>
+      </c>
+      <c r="D1" s="2" t="s">
+        <v>1640</v>
+      </c>
+      <c r="E1" s="2" t="s">
+        <v>1641</v>
+      </c>
+      <c r="F1" s="2" t="s">
+        <v>1616</v>
+      </c>
+      <c r="G1" s="2" t="s">
+        <v>1642</v>
+      </c>
+      <c r="H1" s="2" t="s">
+        <v>1643</v>
+      </c>
+      <c r="I1" s="2" t="s">
+        <v>1644</v>
+      </c>
+      <c r="J1" s="2" t="s">
+        <v>1645</v>
+      </c>
+      <c r="K1" s="2" t="s">
+        <v>1646</v>
+      </c>
+      <c r="L1" s="2" t="s">
+        <v>1647</v>
+      </c>
+      <c r="M1" s="2" t="s">
+        <v>1648</v>
+      </c>
+      <c r="N1" s="2" t="s">
+        <v>1649</v>
+      </c>
+      <c r="O1" s="2" t="s">
+        <v>1603</v>
+      </c>
+      <c r="P1" s="2" t="s">
+        <v>1650</v>
+      </c>
+      <c r="Q1" s="2" t="s">
+        <v>1651</v>
+      </c>
+      <c r="R1" s="2" t="s">
+        <v>1652</v>
+      </c>
+      <c r="S1" s="2" t="s">
+        <v>1653</v>
+      </c>
+      <c r="T1" s="2" t="s">
+        <v>1654</v>
+      </c>
+      <c r="U1" s="2" t="s">
+        <v>1655</v>
+      </c>
+    </row>
+    <row r="2" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A2" s="1">
+        <v>485822412</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1656</v>
+      </c>
+      <c r="C2" s="1" t="s">
+        <v>1657</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>1658</v>
+      </c>
+      <c r="E2" s="1" t="s">
+        <v>1659</v>
+      </c>
+      <c r="F2" s="1" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G2" s="1" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H2" s="1" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J2" s="1" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L2" s="1" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M2" s="1" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N2" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P2" s="1" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q2" s="1" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R2" s="1" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S2" s="1" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T2" s="1" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U2" s="1" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="3" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A3" s="1">
+        <v>494130244</v>
+      </c>
+      <c r="B3" s="1" t="s">
+        <v>1674</v>
+      </c>
+      <c r="C3" s="1" t="s">
+        <v>1675</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>1676</v>
+      </c>
+      <c r="E3" s="1" t="s">
+        <v>1677</v>
+      </c>
+      <c r="F3" s="1" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G3" s="1" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H3" s="1" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I3" s="1" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J3" s="1" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L3" s="1" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M3" s="1" t="s">
+        <v>93</v>
+      </c>
+      <c r="N3" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P3" s="1" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q3" s="1" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R3" s="1" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S3" s="1" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T3" s="1" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U3" s="1" t="s">
+        <v>46</v>
+      </c>
+    </row>
+  </sheetData>
+  <autoFilter ref="A1:U3" xr:uid="{9BB98BCD-633E-4EC9-B3A3-92667D1A84E5}"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
 </file>
--- a/data/payments_incident_sample.xlsx
+++ b/data/payments_incident_sample.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\udita\Documents\Udit Files\code\WU\Dashboard for executive view\data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5C81BF62-8B5B-44C2-A456-B34E3BE3CF56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{66B7DB67-DAC4-419A-BD16-7E1565BDFB0C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="684" windowWidth="17280" windowHeight="8880" activeTab="6" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DATA" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7310" uniqueCount="1690">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="9270" uniqueCount="2180">
   <si>
     <t>Incident</t>
   </si>
@@ -5099,7 +5099,1477 @@
     <t>SBIN</t>
   </si>
   <si>
-    <t>RETURNED</t>
+    <t>PENDING</t>
+  </si>
+  <si>
+    <t>WESTERN UNION</t>
+  </si>
+  <si>
+    <t>6284027113</t>
+  </si>
+  <si>
+    <t>2606115205051775</t>
+  </si>
+  <si>
+    <t>4/4/2026 14:34</t>
+  </si>
+  <si>
+    <t>4/4/2026 16:41</t>
+  </si>
+  <si>
+    <t>04-Apr-26</t>
+  </si>
+  <si>
+    <t>Apr-26</t>
+  </si>
+  <si>
+    <t>AML_CHECK</t>
+  </si>
+  <si>
+    <t>AE</t>
+  </si>
+  <si>
+    <t>SALARY</t>
+  </si>
+  <si>
+    <t>API</t>
+  </si>
+  <si>
+    <t>CHASE BANK</t>
+  </si>
+  <si>
+    <t>CHAS</t>
+  </si>
+  <si>
+    <t>CARD</t>
+  </si>
+  <si>
+    <t>6408157429</t>
+  </si>
+  <si>
+    <t>2663811523004217</t>
+  </si>
+  <si>
+    <t>23/3/2026 11:10</t>
+  </si>
+  <si>
+    <t>23/3/2026 17:29</t>
+  </si>
+  <si>
+    <t>23-Mar-26</t>
+  </si>
+  <si>
+    <t>45|45</t>
+  </si>
+  <si>
+    <t>Routing Code Invalid</t>
+  </si>
+  <si>
+    <t>MASTERCARD</t>
+  </si>
+  <si>
+    <t>MX</t>
+  </si>
+  <si>
+    <t>HDFC BANK</t>
+  </si>
+  <si>
+    <t>HDFC</t>
+  </si>
+  <si>
+    <t>6235809993</t>
+  </si>
+  <si>
+    <t>2645641262883119</t>
+  </si>
+  <si>
+    <t>18/4/2026 01:14</t>
+  </si>
+  <si>
+    <t>18/4/2026 01:46</t>
+  </si>
+  <si>
+    <t>18-Apr-26</t>
+  </si>
+  <si>
+    <t>INVALID_IBAN</t>
+  </si>
+  <si>
+    <t>COMPLETED</t>
+  </si>
+  <si>
+    <t>BRANCH</t>
+  </si>
+  <si>
+    <t>6264814270</t>
+  </si>
+  <si>
+    <t>2679004828145945</t>
+  </si>
+  <si>
+    <t>10/3/2026 08:47</t>
+  </si>
+  <si>
+    <t>10/3/2026 18:45</t>
+  </si>
+  <si>
+    <t>10-Mar-26</t>
+  </si>
+  <si>
+    <t>ACCOUNT_CLOSED</t>
+  </si>
+  <si>
+    <t>PROCESSING</t>
+  </si>
+  <si>
+    <t>6068212356</t>
+  </si>
+  <si>
+    <t>2653705923632197</t>
+  </si>
+  <si>
+    <t>18/3/2026 14:33</t>
+  </si>
+  <si>
+    <t>18/3/2026 18:50</t>
+  </si>
+  <si>
+    <t>18-Mar-26</t>
+  </si>
+  <si>
+    <t>SV</t>
+  </si>
+  <si>
+    <t>6940439931</t>
+  </si>
+  <si>
+    <t>2637068658769419</t>
+  </si>
+  <si>
+    <t>6/3/2026 05:32</t>
+  </si>
+  <si>
+    <t>6/3/2026 07:20</t>
+  </si>
+  <si>
+    <t>06-Mar-26</t>
+  </si>
+  <si>
+    <t>Invalid Account Number</t>
+  </si>
+  <si>
+    <t>6258633898</t>
+  </si>
+  <si>
+    <t>2679851508022456</t>
+  </si>
+  <si>
+    <t>11/1/2026 02:46</t>
+  </si>
+  <si>
+    <t>11/1/2026 11:03</t>
+  </si>
+  <si>
+    <t>11-Jan-26</t>
+  </si>
+  <si>
+    <t>FORMAT_ERROR</t>
+  </si>
+  <si>
+    <t>GB</t>
+  </si>
+  <si>
+    <t>BANCO CUSCATLAN DE EL SALVADOR S.A.</t>
+  </si>
+  <si>
+    <t>BCSV</t>
+  </si>
+  <si>
+    <t>6215984311</t>
+  </si>
+  <si>
+    <t>2643871858053862</t>
+  </si>
+  <si>
+    <t>21/2/2026 21:41</t>
+  </si>
+  <si>
+    <t>22/2/2026 04:03</t>
+  </si>
+  <si>
+    <t>21-Feb-26</t>
+  </si>
+  <si>
+    <t>No IBAN Quoted</t>
+  </si>
+  <si>
+    <t>6677641645</t>
+  </si>
+  <si>
+    <t>2632216802548192</t>
+  </si>
+  <si>
+    <t>9/1/2026 01:55</t>
+  </si>
+  <si>
+    <t>9/1/2026 07:33</t>
+  </si>
+  <si>
+    <t>09-Jan-26</t>
+  </si>
+  <si>
+    <t>6101281557</t>
+  </si>
+  <si>
+    <t>2692741645137195</t>
+  </si>
+  <si>
+    <t>25/2/2026 11:27</t>
+  </si>
+  <si>
+    <t>25/2/2026 18:27</t>
+  </si>
+  <si>
+    <t>25-Feb-26</t>
+  </si>
+  <si>
+    <t>MONEYGRAM</t>
+  </si>
+  <si>
+    <t>6481695135</t>
+  </si>
+  <si>
+    <t>2659374229978292</t>
+  </si>
+  <si>
+    <t>24/1/2026 08:29</t>
+  </si>
+  <si>
+    <t>24/1/2026 12:44</t>
+  </si>
+  <si>
+    <t>24-Jan-26</t>
+  </si>
+  <si>
+    <t>6968990653</t>
+  </si>
+  <si>
+    <t>2623167305431760</t>
+  </si>
+  <si>
+    <t>18/2/2026 00:24</t>
+  </si>
+  <si>
+    <t>18/2/2026 04:55</t>
+  </si>
+  <si>
+    <t>18-Feb-26</t>
+  </si>
+  <si>
+    <t>12|12</t>
+  </si>
+  <si>
+    <t>Transaction Timeout</t>
+  </si>
+  <si>
+    <t>6053839920</t>
+  </si>
+  <si>
+    <t>2667102783089082</t>
+  </si>
+  <si>
+    <t>6/3/2026 16:10</t>
+  </si>
+  <si>
+    <t>6/3/2026 17:08</t>
+  </si>
+  <si>
+    <t>6705849060</t>
+  </si>
+  <si>
+    <t>2679549596142604</t>
+  </si>
+  <si>
+    <t>8/3/2026 10:59</t>
+  </si>
+  <si>
+    <t>8/3/2026 15:26</t>
+  </si>
+  <si>
+    <t>08-Mar-26</t>
+  </si>
+  <si>
+    <t>6107354053</t>
+  </si>
+  <si>
+    <t>2675664753506016</t>
+  </si>
+  <si>
+    <t>28/1/2026 16:16</t>
+  </si>
+  <si>
+    <t>28/1/2026 18:31</t>
+  </si>
+  <si>
+    <t>28-Jan-26</t>
+  </si>
+  <si>
+    <t>BUSINESS</t>
+  </si>
+  <si>
+    <t>6712308209</t>
+  </si>
+  <si>
+    <t>2618901627628997</t>
+  </si>
+  <si>
+    <t>3/2/2026 03:56</t>
+  </si>
+  <si>
+    <t>3/2/2026 05:45</t>
+  </si>
+  <si>
+    <t>03-Feb-26</t>
+  </si>
+  <si>
+    <t>6681057736</t>
+  </si>
+  <si>
+    <t>2606203121107955</t>
+  </si>
+  <si>
+    <t>1/1/2026 10:49</t>
+  </si>
+  <si>
+    <t>1/1/2026 13:02</t>
+  </si>
+  <si>
+    <t>01-Jan-26</t>
+  </si>
+  <si>
+    <t>6159014493</t>
+  </si>
+  <si>
+    <t>2617937629347991</t>
+  </si>
+  <si>
+    <t>6/1/2026 09:23</t>
+  </si>
+  <si>
+    <t>6/1/2026 10:03</t>
+  </si>
+  <si>
+    <t>06-Jan-26</t>
+  </si>
+  <si>
+    <t>6026614158</t>
+  </si>
+  <si>
+    <t>2646754689659649</t>
+  </si>
+  <si>
+    <t>11/4/2026 13:51</t>
+  </si>
+  <si>
+    <t>12/4/2026 01:16</t>
+  </si>
+  <si>
+    <t>11-Apr-26</t>
+  </si>
+  <si>
+    <t>6239362341</t>
+  </si>
+  <si>
+    <t>2692887359348571</t>
+  </si>
+  <si>
+    <t>25/1/2026 12:21</t>
+  </si>
+  <si>
+    <t>25/1/2026 17:06</t>
+  </si>
+  <si>
+    <t>25-Jan-26</t>
+  </si>
+  <si>
+    <t>6466609283</t>
+  </si>
+  <si>
+    <t>2644147051551587</t>
+  </si>
+  <si>
+    <t>25/2/2026 19:32</t>
+  </si>
+  <si>
+    <t>25/2/2026 21:30</t>
+  </si>
+  <si>
+    <t>6910549476</t>
+  </si>
+  <si>
+    <t>2642266343864371</t>
+  </si>
+  <si>
+    <t>6/3/2026 09:42</t>
+  </si>
+  <si>
+    <t>6/3/2026 16:40</t>
+  </si>
+  <si>
+    <t>6326283245</t>
+  </si>
+  <si>
+    <t>2629580672052588</t>
+  </si>
+  <si>
+    <t>25/2/2026 18:38</t>
+  </si>
+  <si>
+    <t>26/2/2026 05:48</t>
+  </si>
+  <si>
+    <t>6333310361</t>
+  </si>
+  <si>
+    <t>2620736957361640</t>
+  </si>
+  <si>
+    <t>4/1/2026 01:15</t>
+  </si>
+  <si>
+    <t>4/1/2026 09:21</t>
+  </si>
+  <si>
+    <t>04-Jan-26</t>
+  </si>
+  <si>
+    <t>6188856883</t>
+  </si>
+  <si>
+    <t>2672897173866028</t>
+  </si>
+  <si>
+    <t>1/3/2026 01:35</t>
+  </si>
+  <si>
+    <t>1/3/2026 05:50</t>
+  </si>
+  <si>
+    <t>01-Mar-26</t>
+  </si>
+  <si>
+    <t>6901795907</t>
+  </si>
+  <si>
+    <t>2639026811586479</t>
+  </si>
+  <si>
+    <t>9/4/2026 16:31</t>
+  </si>
+  <si>
+    <t>10/4/2026 03:12</t>
+  </si>
+  <si>
+    <t>09-Apr-26</t>
+  </si>
+  <si>
+    <t>6745122940</t>
+  </si>
+  <si>
+    <t>2699416264294114</t>
+  </si>
+  <si>
+    <t>28/1/2026 02:26</t>
+  </si>
+  <si>
+    <t>28/1/2026 09:23</t>
+  </si>
+  <si>
+    <t>6320632895</t>
+  </si>
+  <si>
+    <t>2654888623226621</t>
+  </si>
+  <si>
+    <t>20/4/2026 13:34</t>
+  </si>
+  <si>
+    <t>20/4/2026 22:53</t>
+  </si>
+  <si>
+    <t>20-Apr-26</t>
+  </si>
+  <si>
+    <t>6987350298</t>
+  </si>
+  <si>
+    <t>2675173190187897</t>
+  </si>
+  <si>
+    <t>4/1/2026 12:37</t>
+  </si>
+  <si>
+    <t>4/1/2026 22:14</t>
+  </si>
+  <si>
+    <t>6362388455</t>
+  </si>
+  <si>
+    <t>2639158845172324</t>
+  </si>
+  <si>
+    <t>7/4/2026 13:16</t>
+  </si>
+  <si>
+    <t>7/4/2026 14:39</t>
+  </si>
+  <si>
+    <t>07-Apr-26</t>
+  </si>
+  <si>
+    <t>TIMEOUT</t>
+  </si>
+  <si>
+    <t>6667154083</t>
+  </si>
+  <si>
+    <t>2633570118862731</t>
+  </si>
+  <si>
+    <t>17/1/2026 15:42</t>
+  </si>
+  <si>
+    <t>17/1/2026 17:39</t>
+  </si>
+  <si>
+    <t>17-Jan-26</t>
+  </si>
+  <si>
+    <t>6027571992</t>
+  </si>
+  <si>
+    <t>2643907145239734</t>
+  </si>
+  <si>
+    <t>15/3/2026 21:58</t>
+  </si>
+  <si>
+    <t>16/3/2026 04:22</t>
+  </si>
+  <si>
+    <t>15-Mar-26</t>
+  </si>
+  <si>
+    <t>6710303128</t>
+  </si>
+  <si>
+    <t>2609703922711487</t>
+  </si>
+  <si>
+    <t>6/3/2026 20:21</t>
+  </si>
+  <si>
+    <t>6/3/2026 20:33</t>
+  </si>
+  <si>
+    <t>6636164778</t>
+  </si>
+  <si>
+    <t>2645360302363127</t>
+  </si>
+  <si>
+    <t>20/4/2026 07:53</t>
+  </si>
+  <si>
+    <t>20/4/2026 09:21</t>
+  </si>
+  <si>
+    <t>6365436049</t>
+  </si>
+  <si>
+    <t>2698683729059146</t>
+  </si>
+  <si>
+    <t>23/4/2026 08:35</t>
+  </si>
+  <si>
+    <t>23/4/2026 08:45</t>
+  </si>
+  <si>
+    <t>23-Apr-26</t>
+  </si>
+  <si>
+    <t>6237937327</t>
+  </si>
+  <si>
+    <t>2697360055555334</t>
+  </si>
+  <si>
+    <t>1/2/2026 09:42</t>
+  </si>
+  <si>
+    <t>1/2/2026 19:37</t>
+  </si>
+  <si>
+    <t>01-Feb-26</t>
+  </si>
+  <si>
+    <t>6129553265</t>
+  </si>
+  <si>
+    <t>2627104341530399</t>
+  </si>
+  <si>
+    <t>10/2/2026 03:47</t>
+  </si>
+  <si>
+    <t>10/2/2026 12:55</t>
+  </si>
+  <si>
+    <t>10-Feb-26</t>
+  </si>
+  <si>
+    <t>6015191689</t>
+  </si>
+  <si>
+    <t>2675173558530830</t>
+  </si>
+  <si>
+    <t>17/1/2026 08:02</t>
+  </si>
+  <si>
+    <t>17/1/2026 08:57</t>
+  </si>
+  <si>
+    <t>6055165334</t>
+  </si>
+  <si>
+    <t>2667237119123532</t>
+  </si>
+  <si>
+    <t>15/1/2026 02:25</t>
+  </si>
+  <si>
+    <t>15/1/2026 10:48</t>
+  </si>
+  <si>
+    <t>15-Jan-26</t>
+  </si>
+  <si>
+    <t>6975499151</t>
+  </si>
+  <si>
+    <t>2641847767837166</t>
+  </si>
+  <si>
+    <t>21/4/2026 18:27</t>
+  </si>
+  <si>
+    <t>21/4/2026 23:39</t>
+  </si>
+  <si>
+    <t>21-Apr-26</t>
+  </si>
+  <si>
+    <t>6080600295</t>
+  </si>
+  <si>
+    <t>2600374334457242</t>
+  </si>
+  <si>
+    <t>22/2/2026 14:44</t>
+  </si>
+  <si>
+    <t>23/2/2026 00:52</t>
+  </si>
+  <si>
+    <t>22-Feb-26</t>
+  </si>
+  <si>
+    <t>6863187150</t>
+  </si>
+  <si>
+    <t>2627843988088189</t>
+  </si>
+  <si>
+    <t>24/2/2026 03:34</t>
+  </si>
+  <si>
+    <t>24/2/2026 07:24</t>
+  </si>
+  <si>
+    <t>24-Feb-26</t>
+  </si>
+  <si>
+    <t>6326515425</t>
+  </si>
+  <si>
+    <t>2656649329000225</t>
+  </si>
+  <si>
+    <t>1/5/2026 08:32</t>
+  </si>
+  <si>
+    <t>1/5/2026 17:44</t>
+  </si>
+  <si>
+    <t>01-May-26</t>
+  </si>
+  <si>
+    <t>May-26</t>
+  </si>
+  <si>
+    <t>6630418447</t>
+  </si>
+  <si>
+    <t>2602920366389972</t>
+  </si>
+  <si>
+    <t>8/4/2026 21:52</t>
+  </si>
+  <si>
+    <t>9/4/2026 02:27</t>
+  </si>
+  <si>
+    <t>08-Apr-26</t>
+  </si>
+  <si>
+    <t>6357887167</t>
+  </si>
+  <si>
+    <t>2694310270820285</t>
+  </si>
+  <si>
+    <t>14/1/2026 05:21</t>
+  </si>
+  <si>
+    <t>14/1/2026 12:22</t>
+  </si>
+  <si>
+    <t>14-Jan-26</t>
+  </si>
+  <si>
+    <t>6706157458</t>
+  </si>
+  <si>
+    <t>2676363957460491</t>
+  </si>
+  <si>
+    <t>1/3/2026 13:03</t>
+  </si>
+  <si>
+    <t>1/3/2026 16:15</t>
+  </si>
+  <si>
+    <t>6130380269</t>
+  </si>
+  <si>
+    <t>2685691598447554</t>
+  </si>
+  <si>
+    <t>13/4/2026 07:45</t>
+  </si>
+  <si>
+    <t>13/4/2026 10:27</t>
+  </si>
+  <si>
+    <t>13-Apr-26</t>
+  </si>
+  <si>
+    <t>6757429971</t>
+  </si>
+  <si>
+    <t>2658472859118723</t>
+  </si>
+  <si>
+    <t>17/4/2026 15:30</t>
+  </si>
+  <si>
+    <t>17/4/2026 19:39</t>
+  </si>
+  <si>
+    <t>17-Apr-26</t>
+  </si>
+  <si>
+    <t>6899232921</t>
+  </si>
+  <si>
+    <t>2681615489436909</t>
+  </si>
+  <si>
+    <t>26/3/2026 15:55</t>
+  </si>
+  <si>
+    <t>26/3/2026 18:27</t>
+  </si>
+  <si>
+    <t>26-Mar-26</t>
+  </si>
+  <si>
+    <t>6341639230</t>
+  </si>
+  <si>
+    <t>2666566601637681</t>
+  </si>
+  <si>
+    <t>1/4/2026 12:24</t>
+  </si>
+  <si>
+    <t>1/4/2026 23:43</t>
+  </si>
+  <si>
+    <t>01-Apr-26</t>
+  </si>
+  <si>
+    <t>6935157154</t>
+  </si>
+  <si>
+    <t>2610527627818895</t>
+  </si>
+  <si>
+    <t>2/3/2026 08:21</t>
+  </si>
+  <si>
+    <t>2/3/2026 18:59</t>
+  </si>
+  <si>
+    <t>02-Mar-26</t>
+  </si>
+  <si>
+    <t>6244261532</t>
+  </si>
+  <si>
+    <t>2612720605500576</t>
+  </si>
+  <si>
+    <t>25/2/2026 03:48</t>
+  </si>
+  <si>
+    <t>25/2/2026 14:36</t>
+  </si>
+  <si>
+    <t>6262204999</t>
+  </si>
+  <si>
+    <t>2657992929772570</t>
+  </si>
+  <si>
+    <t>14/3/2026 21:50</t>
+  </si>
+  <si>
+    <t>15/3/2026 00:54</t>
+  </si>
+  <si>
+    <t>14-Mar-26</t>
+  </si>
+  <si>
+    <t>6274154962</t>
+  </si>
+  <si>
+    <t>2601321419018953</t>
+  </si>
+  <si>
+    <t>26/4/2026 14:57</t>
+  </si>
+  <si>
+    <t>26/4/2026 19:51</t>
+  </si>
+  <si>
+    <t>26-Apr-26</t>
+  </si>
+  <si>
+    <t>6114518079</t>
+  </si>
+  <si>
+    <t>2653670930121552</t>
+  </si>
+  <si>
+    <t>15/3/2026 11:36</t>
+  </si>
+  <si>
+    <t>15/3/2026 16:38</t>
+  </si>
+  <si>
+    <t>6235154329</t>
+  </si>
+  <si>
+    <t>2626760380507043</t>
+  </si>
+  <si>
+    <t>21/3/2026 08:43</t>
+  </si>
+  <si>
+    <t>21/3/2026 19:58</t>
+  </si>
+  <si>
+    <t>21-Mar-26</t>
+  </si>
+  <si>
+    <t>6802601465</t>
+  </si>
+  <si>
+    <t>2624719321360672</t>
+  </si>
+  <si>
+    <t>26/1/2026 04:50</t>
+  </si>
+  <si>
+    <t>26/1/2026 14:02</t>
+  </si>
+  <si>
+    <t>26-Jan-26</t>
+  </si>
+  <si>
+    <t>6724138175</t>
+  </si>
+  <si>
+    <t>2655933272948387</t>
+  </si>
+  <si>
+    <t>19/4/2026 17:23</t>
+  </si>
+  <si>
+    <t>19/4/2026 18:55</t>
+  </si>
+  <si>
+    <t>19-Apr-26</t>
+  </si>
+  <si>
+    <t>6724600232</t>
+  </si>
+  <si>
+    <t>2666353954013342</t>
+  </si>
+  <si>
+    <t>4/1/2026 19:56</t>
+  </si>
+  <si>
+    <t>5/1/2026 05:30</t>
+  </si>
+  <si>
+    <t>6104359116</t>
+  </si>
+  <si>
+    <t>2619093438375810</t>
+  </si>
+  <si>
+    <t>19/2/2026 14:23</t>
+  </si>
+  <si>
+    <t>20/2/2026 01:49</t>
+  </si>
+  <si>
+    <t>19-Feb-26</t>
+  </si>
+  <si>
+    <t>6233291547</t>
+  </si>
+  <si>
+    <t>2662583872785871</t>
+  </si>
+  <si>
+    <t>31/1/2026 11:06</t>
+  </si>
+  <si>
+    <t>31/1/2026 22:48</t>
+  </si>
+  <si>
+    <t>31-Jan-26</t>
+  </si>
+  <si>
+    <t>6135209737</t>
+  </si>
+  <si>
+    <t>2679460275021208</t>
+  </si>
+  <si>
+    <t>27/1/2026 02:53</t>
+  </si>
+  <si>
+    <t>27/1/2026 12:20</t>
+  </si>
+  <si>
+    <t>27-Jan-26</t>
+  </si>
+  <si>
+    <t>6141522640</t>
+  </si>
+  <si>
+    <t>2650414389945059</t>
+  </si>
+  <si>
+    <t>12/4/2026 07:37</t>
+  </si>
+  <si>
+    <t>12/4/2026 13:08</t>
+  </si>
+  <si>
+    <t>12-Apr-26</t>
+  </si>
+  <si>
+    <t>6117095851</t>
+  </si>
+  <si>
+    <t>2670907556438171</t>
+  </si>
+  <si>
+    <t>29/1/2026 19:02</t>
+  </si>
+  <si>
+    <t>30/1/2026 06:16</t>
+  </si>
+  <si>
+    <t>6965580338</t>
+  </si>
+  <si>
+    <t>2645329431834460</t>
+  </si>
+  <si>
+    <t>19/3/2026 04:04</t>
+  </si>
+  <si>
+    <t>19/3/2026 06:13</t>
+  </si>
+  <si>
+    <t>19-Mar-26</t>
+  </si>
+  <si>
+    <t>6444328940</t>
+  </si>
+  <si>
+    <t>2656115695485193</t>
+  </si>
+  <si>
+    <t>23/2/2026 23:06</t>
+  </si>
+  <si>
+    <t>24/2/2026 04:26</t>
+  </si>
+  <si>
+    <t>23-Feb-26</t>
+  </si>
+  <si>
+    <t>6793276164</t>
+  </si>
+  <si>
+    <t>2678302107614994</t>
+  </si>
+  <si>
+    <t>8/1/2026 18:35</t>
+  </si>
+  <si>
+    <t>9/1/2026 04:10</t>
+  </si>
+  <si>
+    <t>08-Jan-26</t>
+  </si>
+  <si>
+    <t>6166140258</t>
+  </si>
+  <si>
+    <t>2667863303937731</t>
+  </si>
+  <si>
+    <t>29/1/2026 03:22</t>
+  </si>
+  <si>
+    <t>29/1/2026 12:51</t>
+  </si>
+  <si>
+    <t>6818630985</t>
+  </si>
+  <si>
+    <t>2649402173374393</t>
+  </si>
+  <si>
+    <t>1/1/2026 05:55</t>
+  </si>
+  <si>
+    <t>1/1/2026 08:21</t>
+  </si>
+  <si>
+    <t>6774807770</t>
+  </si>
+  <si>
+    <t>2679881845085095</t>
+  </si>
+  <si>
+    <t>18/3/2026 02:56</t>
+  </si>
+  <si>
+    <t>18/3/2026 03:49</t>
+  </si>
+  <si>
+    <t>6810614025</t>
+  </si>
+  <si>
+    <t>2616018133557431</t>
+  </si>
+  <si>
+    <t>14/2/2026 13:07</t>
+  </si>
+  <si>
+    <t>14/2/2026 17:57</t>
+  </si>
+  <si>
+    <t>14-Feb-26</t>
+  </si>
+  <si>
+    <t>6823935280</t>
+  </si>
+  <si>
+    <t>2640734567283196</t>
+  </si>
+  <si>
+    <t>11/2/2026 03:00</t>
+  </si>
+  <si>
+    <t>11/2/2026 11:29</t>
+  </si>
+  <si>
+    <t>11-Feb-26</t>
+  </si>
+  <si>
+    <t>6925683580</t>
+  </si>
+  <si>
+    <t>2681030197591494</t>
+  </si>
+  <si>
+    <t>24/2/2026 18:25</t>
+  </si>
+  <si>
+    <t>25/2/2026 05:20</t>
+  </si>
+  <si>
+    <t>6467804106</t>
+  </si>
+  <si>
+    <t>2656356795073744</t>
+  </si>
+  <si>
+    <t>9/3/2026 02:25</t>
+  </si>
+  <si>
+    <t>9/3/2026 07:42</t>
+  </si>
+  <si>
+    <t>09-Mar-26</t>
+  </si>
+  <si>
+    <t>6211818984</t>
+  </si>
+  <si>
+    <t>2684779104628378</t>
+  </si>
+  <si>
+    <t>20/1/2026 20:04</t>
+  </si>
+  <si>
+    <t>20/1/2026 23:05</t>
+  </si>
+  <si>
+    <t>20-Jan-26</t>
+  </si>
+  <si>
+    <t>6855052486</t>
+  </si>
+  <si>
+    <t>2683233350943591</t>
+  </si>
+  <si>
+    <t>8/1/2026 11:32</t>
+  </si>
+  <si>
+    <t>8/1/2026 12:47</t>
+  </si>
+  <si>
+    <t>6850207886</t>
+  </si>
+  <si>
+    <t>2663290814265068</t>
+  </si>
+  <si>
+    <t>27/4/2026 18:41</t>
+  </si>
+  <si>
+    <t>27/4/2026 21:53</t>
+  </si>
+  <si>
+    <t>27-Apr-26</t>
+  </si>
+  <si>
+    <t>6470039364</t>
+  </si>
+  <si>
+    <t>2661843195380382</t>
+  </si>
+  <si>
+    <t>9/3/2026 16:39</t>
+  </si>
+  <si>
+    <t>9/3/2026 19:21</t>
+  </si>
+  <si>
+    <t>6728404274</t>
+  </si>
+  <si>
+    <t>2639987805806379</t>
+  </si>
+  <si>
+    <t>2/2/2026 23:54</t>
+  </si>
+  <si>
+    <t>3/2/2026 11:06</t>
+  </si>
+  <si>
+    <t>02-Feb-26</t>
+  </si>
+  <si>
+    <t>6332411019</t>
+  </si>
+  <si>
+    <t>2653015181886537</t>
+  </si>
+  <si>
+    <t>24/3/2026 10:52</t>
+  </si>
+  <si>
+    <t>24/3/2026 13:02</t>
+  </si>
+  <si>
+    <t>24-Mar-26</t>
+  </si>
+  <si>
+    <t>6243248743</t>
+  </si>
+  <si>
+    <t>2619361712469960</t>
+  </si>
+  <si>
+    <t>20/1/2026 02:18</t>
+  </si>
+  <si>
+    <t>20/1/2026 04:01</t>
+  </si>
+  <si>
+    <t>6726239153</t>
+  </si>
+  <si>
+    <t>2633430821061704</t>
+  </si>
+  <si>
+    <t>26/2/2026 19:18</t>
+  </si>
+  <si>
+    <t>27/2/2026 02:57</t>
+  </si>
+  <si>
+    <t>26-Feb-26</t>
+  </si>
+  <si>
+    <t>6148604290</t>
+  </si>
+  <si>
+    <t>2635188121603543</t>
+  </si>
+  <si>
+    <t>7/1/2026 20:30</t>
+  </si>
+  <si>
+    <t>8/1/2026 02:50</t>
+  </si>
+  <si>
+    <t>07-Jan-26</t>
+  </si>
+  <si>
+    <t>6876928440</t>
+  </si>
+  <si>
+    <t>2658390194936723</t>
+  </si>
+  <si>
+    <t>7/1/2026 12:32</t>
+  </si>
+  <si>
+    <t>7/1/2026 18:54</t>
+  </si>
+  <si>
+    <t>6985046632</t>
+  </si>
+  <si>
+    <t>2666493952508253</t>
+  </si>
+  <si>
+    <t>31/3/2026 04:48</t>
+  </si>
+  <si>
+    <t>31/3/2026 12:48</t>
+  </si>
+  <si>
+    <t>31-Mar-26</t>
+  </si>
+  <si>
+    <t>6130833665</t>
+  </si>
+  <si>
+    <t>2633556784565959</t>
+  </si>
+  <si>
+    <t>23/2/2026 20:50</t>
+  </si>
+  <si>
+    <t>24/2/2026 07:27</t>
+  </si>
+  <si>
+    <t>6201126777</t>
+  </si>
+  <si>
+    <t>2694045457366232</t>
+  </si>
+  <si>
+    <t>11/1/2026 16:23</t>
+  </si>
+  <si>
+    <t>11/1/2026 17:32</t>
+  </si>
+  <si>
+    <t>6786989426</t>
+  </si>
+  <si>
+    <t>2688419018997352</t>
+  </si>
+  <si>
+    <t>14/1/2026 18:47</t>
+  </si>
+  <si>
+    <t>15/1/2026 00:27</t>
+  </si>
+  <si>
+    <t>6039711044</t>
+  </si>
+  <si>
+    <t>2628369519316347</t>
+  </si>
+  <si>
+    <t>6/1/2026 06:56</t>
+  </si>
+  <si>
+    <t>6/1/2026 07:38</t>
+  </si>
+  <si>
+    <t>6293364102</t>
+  </si>
+  <si>
+    <t>2661496922374439</t>
+  </si>
+  <si>
+    <t>24/4/2026 12:47</t>
+  </si>
+  <si>
+    <t>24/4/2026 20:17</t>
+  </si>
+  <si>
+    <t>24-Apr-26</t>
+  </si>
+  <si>
+    <t>6585698675</t>
+  </si>
+  <si>
+    <t>2645205792507580</t>
+  </si>
+  <si>
+    <t>14/1/2026 02:20</t>
+  </si>
+  <si>
+    <t>14/1/2026 13:36</t>
+  </si>
+  <si>
+    <t>6686624943</t>
+  </si>
+  <si>
+    <t>2608074314767498</t>
+  </si>
+  <si>
+    <t>10/1/2026 21:40</t>
+  </si>
+  <si>
+    <t>11/1/2026 04:35</t>
+  </si>
+  <si>
+    <t>10-Jan-26</t>
+  </si>
+  <si>
+    <t>6649715626</t>
+  </si>
+  <si>
+    <t>2695567976315196</t>
+  </si>
+  <si>
+    <t>27/2/2026 11:23</t>
+  </si>
+  <si>
+    <t>27/2/2026 18:57</t>
+  </si>
+  <si>
+    <t>6980908797</t>
+  </si>
+  <si>
+    <t>2616572396193899</t>
+  </si>
+  <si>
+    <t>3/2/2026 08:45</t>
+  </si>
+  <si>
+    <t>3/2/2026 16:21</t>
+  </si>
+  <si>
+    <t>6717087513</t>
+  </si>
+  <si>
+    <t>2699859481812259</t>
+  </si>
+  <si>
+    <t>9/1/2026 17:34</t>
+  </si>
+  <si>
+    <t>9/1/2026 22:31</t>
+  </si>
+  <si>
+    <t>6594875990</t>
+  </si>
+  <si>
+    <t>2651920022586794</t>
+  </si>
+  <si>
+    <t>1/3/2026 17:08</t>
+  </si>
+  <si>
+    <t>2/3/2026 03:34</t>
+  </si>
+  <si>
+    <t>6500184588</t>
+  </si>
+  <si>
+    <t>2672811206647657</t>
+  </si>
+  <si>
+    <t>14/2/2026 04:56</t>
+  </si>
+  <si>
+    <t>14/2/2026 14:20</t>
+  </si>
+  <si>
+    <t>6557162259</t>
+  </si>
+  <si>
+    <t>2639977104301438</t>
+  </si>
+  <si>
+    <t>19/4/2026 02:16</t>
+  </si>
+  <si>
+    <t>19/4/2026 05:37</t>
   </si>
 </sst>
 </file>
@@ -5163,10 +6633,9 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -27773,202 +29242,6572 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9BB98BCD-633E-4EC9-B3A3-92667D1A84E5}">
-  <dimension ref="A1:U3"/>
+  <dimension ref="A1:U101"/>
   <sheetFormatPr defaultRowHeight="15.6" x14ac:dyDescent="0.3"/>
   <sheetData>
     <row r="1" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A1" s="2" t="s">
+      <c r="A1" s="1" t="s">
         <v>1637</v>
       </c>
-      <c r="B1" s="2" t="s">
+      <c r="B1" s="1" t="s">
         <v>1638</v>
       </c>
-      <c r="C1" s="2" t="s">
+      <c r="C1" s="1" t="s">
         <v>1639</v>
       </c>
-      <c r="D1" s="2" t="s">
+      <c r="D1" s="1" t="s">
         <v>1640</v>
       </c>
-      <c r="E1" s="2" t="s">
+      <c r="E1" s="1" t="s">
         <v>1641</v>
       </c>
-      <c r="F1" s="2" t="s">
+      <c r="F1" s="1" t="s">
         <v>1616</v>
       </c>
-      <c r="G1" s="2" t="s">
+      <c r="G1" s="1" t="s">
         <v>1642</v>
       </c>
-      <c r="H1" s="2" t="s">
+      <c r="H1" s="1" t="s">
         <v>1643</v>
       </c>
-      <c r="I1" s="2" t="s">
+      <c r="I1" s="1" t="s">
         <v>1644</v>
       </c>
-      <c r="J1" s="2" t="s">
+      <c r="J1" s="1" t="s">
         <v>1645</v>
       </c>
-      <c r="K1" s="2" t="s">
+      <c r="K1" s="1" t="s">
         <v>1646</v>
       </c>
-      <c r="L1" s="2" t="s">
+      <c r="L1" s="1" t="s">
         <v>1647</v>
       </c>
-      <c r="M1" s="2" t="s">
+      <c r="M1" s="1" t="s">
         <v>1648</v>
       </c>
-      <c r="N1" s="2" t="s">
+      <c r="N1" s="1" t="s">
         <v>1649</v>
       </c>
-      <c r="O1" s="2" t="s">
+      <c r="O1" s="1" t="s">
         <v>1603</v>
       </c>
-      <c r="P1" s="2" t="s">
+      <c r="P1" s="1" t="s">
         <v>1650</v>
       </c>
-      <c r="Q1" s="2" t="s">
+      <c r="Q1" s="1" t="s">
         <v>1651</v>
       </c>
-      <c r="R1" s="2" t="s">
+      <c r="R1" s="1" t="s">
         <v>1652</v>
       </c>
-      <c r="S1" s="2" t="s">
+      <c r="S1" s="1" t="s">
         <v>1653</v>
       </c>
-      <c r="T1" s="2" t="s">
+      <c r="T1" s="1" t="s">
         <v>1654</v>
       </c>
-      <c r="U1" s="2" t="s">
+      <c r="U1" s="1" t="s">
         <v>1655</v>
       </c>
     </row>
     <row r="2" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A2" s="1">
+      <c r="A2">
         <v>485822412</v>
       </c>
-      <c r="B2" s="1" t="s">
+      <c r="B2" t="s">
         <v>1656</v>
       </c>
-      <c r="C2" s="1" t="s">
+      <c r="C2" t="s">
         <v>1657</v>
       </c>
-      <c r="D2" s="1" t="s">
+      <c r="D2" t="s">
         <v>1658</v>
       </c>
-      <c r="E2" s="1" t="s">
+      <c r="E2" t="s">
         <v>1659</v>
       </c>
-      <c r="F2" s="1" t="s">
+      <c r="F2" t="s">
         <v>1660</v>
       </c>
-      <c r="G2" s="1" t="s">
+      <c r="G2" t="s">
         <v>1618</v>
       </c>
-      <c r="H2" s="1" t="s">
+      <c r="H2" t="s">
         <v>1661</v>
       </c>
-      <c r="I2" s="1" t="s">
+      <c r="I2" t="s">
         <v>1662</v>
       </c>
-      <c r="J2" s="1" t="s">
+      <c r="J2" t="s">
         <v>1663</v>
       </c>
-      <c r="K2" s="1" t="s">
+      <c r="K2" t="s">
         <v>1664</v>
       </c>
-      <c r="L2" s="1" t="s">
+      <c r="L2" t="s">
         <v>1665</v>
       </c>
-      <c r="M2" s="1" t="s">
+      <c r="M2" t="s">
         <v>1666</v>
       </c>
-      <c r="N2" s="1" t="s">
+      <c r="N2" t="s">
         <v>1667</v>
       </c>
-      <c r="O2" s="1" t="s">
+      <c r="O2" t="s">
         <v>1667</v>
       </c>
-      <c r="P2" s="1" t="s">
+      <c r="P2" t="s">
         <v>1668</v>
       </c>
-      <c r="Q2" s="1" t="s">
+      <c r="Q2" t="s">
         <v>1669</v>
       </c>
-      <c r="R2" s="1" t="s">
+      <c r="R2" t="s">
         <v>1670</v>
       </c>
-      <c r="S2" s="1" t="s">
+      <c r="S2" t="s">
         <v>1671</v>
       </c>
-      <c r="T2" s="1" t="s">
+      <c r="T2" t="s">
         <v>1672</v>
       </c>
-      <c r="U2" s="1" t="s">
+      <c r="U2" t="s">
         <v>1673</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.3">
-      <c r="A3" s="1">
+      <c r="A3">
         <v>494130244</v>
       </c>
-      <c r="B3" s="1" t="s">
+      <c r="B3" t="s">
         <v>1674</v>
       </c>
-      <c r="C3" s="1" t="s">
+      <c r="C3" t="s">
         <v>1675</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" t="s">
         <v>1676</v>
       </c>
-      <c r="E3" s="1" t="s">
+      <c r="E3" t="s">
         <v>1677</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" t="s">
         <v>1678</v>
       </c>
-      <c r="G3" s="1" t="s">
+      <c r="G3" t="s">
         <v>1620</v>
       </c>
-      <c r="H3" s="1" t="s">
+      <c r="H3" t="s">
         <v>1679</v>
       </c>
-      <c r="I3" s="1" t="s">
+      <c r="I3" t="s">
         <v>1680</v>
       </c>
-      <c r="J3" s="1" t="s">
+      <c r="J3" t="s">
         <v>1681</v>
       </c>
-      <c r="K3" s="1" t="s">
+      <c r="K3" t="s">
         <v>1682</v>
       </c>
-      <c r="L3" s="1" t="s">
+      <c r="L3" t="s">
         <v>1689</v>
       </c>
-      <c r="M3" s="1" t="s">
-        <v>93</v>
-      </c>
-      <c r="N3" s="1" t="s">
+      <c r="M3" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N3" t="s">
         <v>1683</v>
       </c>
-      <c r="O3" s="1" t="s">
+      <c r="O3" t="s">
         <v>1683</v>
       </c>
-      <c r="P3" s="1" t="s">
+      <c r="P3" t="s">
         <v>1684</v>
       </c>
-      <c r="Q3" s="1" t="s">
+      <c r="Q3" t="s">
         <v>1685</v>
       </c>
-      <c r="R3" s="1" t="s">
+      <c r="R3" t="s">
         <v>1686</v>
       </c>
-      <c r="S3" s="1" t="s">
+      <c r="S3" t="s">
         <v>1687</v>
       </c>
-      <c r="T3" s="1" t="s">
+      <c r="T3" t="s">
         <v>1688</v>
       </c>
-      <c r="U3" s="1" t="s">
+      <c r="U3" t="s">
         <v>46</v>
+      </c>
+    </row>
+    <row r="4" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A4">
+        <v>481030736</v>
+      </c>
+      <c r="B4" t="s">
+        <v>1691</v>
+      </c>
+      <c r="C4" t="s">
+        <v>1692</v>
+      </c>
+      <c r="D4" t="s">
+        <v>1693</v>
+      </c>
+      <c r="E4" t="s">
+        <v>1694</v>
+      </c>
+      <c r="F4" t="s">
+        <v>1695</v>
+      </c>
+      <c r="G4" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H4" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I4" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J4" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K4" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L4" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M4" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N4" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O4" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P4" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q4" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R4" t="s">
+        <v>111</v>
+      </c>
+      <c r="S4" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T4" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U4" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="5" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A5">
+        <v>413556182</v>
+      </c>
+      <c r="B5" t="s">
+        <v>1704</v>
+      </c>
+      <c r="C5" t="s">
+        <v>1705</v>
+      </c>
+      <c r="D5" t="s">
+        <v>1706</v>
+      </c>
+      <c r="E5" t="s">
+        <v>1707</v>
+      </c>
+      <c r="F5" t="s">
+        <v>1708</v>
+      </c>
+      <c r="G5" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H5" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I5" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J5" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K5" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L5" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M5" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N5" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O5" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P5" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R5" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S5" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T5" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U5" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="6" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A6">
+        <v>474752529</v>
+      </c>
+      <c r="B6" t="s">
+        <v>1715</v>
+      </c>
+      <c r="C6" t="s">
+        <v>1716</v>
+      </c>
+      <c r="D6" t="s">
+        <v>1717</v>
+      </c>
+      <c r="E6" t="s">
+        <v>1718</v>
+      </c>
+      <c r="F6" t="s">
+        <v>1719</v>
+      </c>
+      <c r="G6" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H6" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I6" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J6" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K6" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L6" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M6" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N6" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O6" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P6" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R6" t="s">
+        <v>111</v>
+      </c>
+      <c r="S6" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T6" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U6" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="7" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A7">
+        <v>418740864</v>
+      </c>
+      <c r="B7" t="s">
+        <v>1723</v>
+      </c>
+      <c r="C7" t="s">
+        <v>1724</v>
+      </c>
+      <c r="D7" t="s">
+        <v>1725</v>
+      </c>
+      <c r="E7" t="s">
+        <v>1726</v>
+      </c>
+      <c r="F7" t="s">
+        <v>1727</v>
+      </c>
+      <c r="G7" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H7" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I7" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J7" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K7" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L7" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M7" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N7" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O7" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P7" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q7" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R7" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S7" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T7" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U7" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="8" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A8">
+        <v>480048665</v>
+      </c>
+      <c r="B8" t="s">
+        <v>1730</v>
+      </c>
+      <c r="C8" t="s">
+        <v>1731</v>
+      </c>
+      <c r="D8" t="s">
+        <v>1732</v>
+      </c>
+      <c r="E8" t="s">
+        <v>1733</v>
+      </c>
+      <c r="F8" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G8" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H8" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I8" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J8" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K8" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L8" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M8" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N8" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O8" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P8" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q8" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R8" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S8" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T8" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U8" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="9" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A9">
+        <v>496917555</v>
+      </c>
+      <c r="B9" t="s">
+        <v>1736</v>
+      </c>
+      <c r="C9" t="s">
+        <v>1737</v>
+      </c>
+      <c r="D9" t="s">
+        <v>1738</v>
+      </c>
+      <c r="E9" t="s">
+        <v>1739</v>
+      </c>
+      <c r="F9" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G9" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H9" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I9" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J9" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K9" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L9" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M9" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N9" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O9" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P9" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q9" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R9" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S9" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T9" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U9" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="10" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A10">
+        <v>407774584</v>
+      </c>
+      <c r="B10" t="s">
+        <v>1742</v>
+      </c>
+      <c r="C10" t="s">
+        <v>1743</v>
+      </c>
+      <c r="D10" t="s">
+        <v>1744</v>
+      </c>
+      <c r="E10" t="s">
+        <v>1745</v>
+      </c>
+      <c r="F10" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G10" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H10" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I10" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J10" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K10" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L10" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M10" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N10" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O10" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P10" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q10" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R10" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S10" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T10" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U10" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="11" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A11">
+        <v>492592466</v>
+      </c>
+      <c r="B11" t="s">
+        <v>1751</v>
+      </c>
+      <c r="C11" t="s">
+        <v>1752</v>
+      </c>
+      <c r="D11" t="s">
+        <v>1753</v>
+      </c>
+      <c r="E11" t="s">
+        <v>1754</v>
+      </c>
+      <c r="F11" t="s">
+        <v>1755</v>
+      </c>
+      <c r="G11" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H11" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I11" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J11" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K11" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L11" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M11" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N11" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O11" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P11" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q11" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R11" t="s">
+        <v>111</v>
+      </c>
+      <c r="S11" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T11" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U11" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="12" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A12">
+        <v>495004803</v>
+      </c>
+      <c r="B12" t="s">
+        <v>1757</v>
+      </c>
+      <c r="C12" t="s">
+        <v>1758</v>
+      </c>
+      <c r="D12" t="s">
+        <v>1759</v>
+      </c>
+      <c r="E12" t="s">
+        <v>1760</v>
+      </c>
+      <c r="F12" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G12" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H12" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I12" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J12" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K12" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L12" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M12" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N12" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O12" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P12" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q12" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R12" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S12" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T12" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U12" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="13" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A13">
+        <v>425556386</v>
+      </c>
+      <c r="B13" t="s">
+        <v>1762</v>
+      </c>
+      <c r="C13" t="s">
+        <v>1763</v>
+      </c>
+      <c r="D13" t="s">
+        <v>1764</v>
+      </c>
+      <c r="E13" t="s">
+        <v>1765</v>
+      </c>
+      <c r="F13" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G13" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H13" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I13" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J13" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K13" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L13" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M13" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N13" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O13" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P13" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q13" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R13" t="s">
+        <v>111</v>
+      </c>
+      <c r="S13" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T13" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U13" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="14" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A14">
+        <v>471979055</v>
+      </c>
+      <c r="B14" t="s">
+        <v>1768</v>
+      </c>
+      <c r="C14" t="s">
+        <v>1769</v>
+      </c>
+      <c r="D14" t="s">
+        <v>1770</v>
+      </c>
+      <c r="E14" t="s">
+        <v>1771</v>
+      </c>
+      <c r="F14" t="s">
+        <v>1772</v>
+      </c>
+      <c r="G14" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H14" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I14" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J14" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K14" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L14" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M14" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N14" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O14" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P14" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q14" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R14" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S14" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T14" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U14" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="15" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A15">
+        <v>453826716</v>
+      </c>
+      <c r="B15" t="s">
+        <v>1773</v>
+      </c>
+      <c r="C15" t="s">
+        <v>1774</v>
+      </c>
+      <c r="D15" t="s">
+        <v>1775</v>
+      </c>
+      <c r="E15" t="s">
+        <v>1776</v>
+      </c>
+      <c r="F15" t="s">
+        <v>1777</v>
+      </c>
+      <c r="G15" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H15" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I15" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J15" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K15" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L15" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M15" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N15" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O15" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P15" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q15" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R15" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S15" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T15" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U15" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="16" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A16">
+        <v>407672593</v>
+      </c>
+      <c r="B16" t="s">
+        <v>1780</v>
+      </c>
+      <c r="C16" t="s">
+        <v>1781</v>
+      </c>
+      <c r="D16" t="s">
+        <v>1782</v>
+      </c>
+      <c r="E16" t="s">
+        <v>1783</v>
+      </c>
+      <c r="F16" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G16" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H16" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I16" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J16" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K16" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L16" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M16" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N16" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O16" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P16" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q16" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R16" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S16" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T16" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U16" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="17" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A17">
+        <v>456267415</v>
+      </c>
+      <c r="B17" t="s">
+        <v>1784</v>
+      </c>
+      <c r="C17" t="s">
+        <v>1785</v>
+      </c>
+      <c r="D17" t="s">
+        <v>1786</v>
+      </c>
+      <c r="E17" t="s">
+        <v>1787</v>
+      </c>
+      <c r="F17" t="s">
+        <v>1788</v>
+      </c>
+      <c r="G17" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H17" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I17" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J17" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K17" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L17" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M17" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N17" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O17" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P17" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q17" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R17" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S17" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T17" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U17" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="18" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A18">
+        <v>475563727</v>
+      </c>
+      <c r="B18" t="s">
+        <v>1789</v>
+      </c>
+      <c r="C18" t="s">
+        <v>1790</v>
+      </c>
+      <c r="D18" t="s">
+        <v>1791</v>
+      </c>
+      <c r="E18" t="s">
+        <v>1792</v>
+      </c>
+      <c r="F18" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G18" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H18" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I18" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J18" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K18" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L18" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M18" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N18" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O18" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P18" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q18" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R18" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S18" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T18" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U18" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="19" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A19">
+        <v>440181935</v>
+      </c>
+      <c r="B19" t="s">
+        <v>1795</v>
+      </c>
+      <c r="C19" t="s">
+        <v>1796</v>
+      </c>
+      <c r="D19" t="s">
+        <v>1797</v>
+      </c>
+      <c r="E19" t="s">
+        <v>1798</v>
+      </c>
+      <c r="F19" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G19" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H19" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I19" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J19" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K19" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L19" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M19" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N19" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O19" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P19" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q19" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R19" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S19" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T19" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U19" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="20" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A20">
+        <v>412388090</v>
+      </c>
+      <c r="B20" t="s">
+        <v>1800</v>
+      </c>
+      <c r="C20" t="s">
+        <v>1801</v>
+      </c>
+      <c r="D20" t="s">
+        <v>1802</v>
+      </c>
+      <c r="E20" t="s">
+        <v>1803</v>
+      </c>
+      <c r="F20" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G20" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H20" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I20" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J20" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K20" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L20" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M20" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N20" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O20" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P20" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q20" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R20" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S20" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T20" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U20" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="21" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A21">
+        <v>474158663</v>
+      </c>
+      <c r="B21" t="s">
+        <v>1805</v>
+      </c>
+      <c r="C21" t="s">
+        <v>1806</v>
+      </c>
+      <c r="D21" t="s">
+        <v>1807</v>
+      </c>
+      <c r="E21" t="s">
+        <v>1808</v>
+      </c>
+      <c r="F21" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G21" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H21" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I21" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J21" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K21" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L21" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M21" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N21" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O21" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P21" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q21" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R21" t="s">
+        <v>111</v>
+      </c>
+      <c r="S21" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T21" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U21" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="22" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A22">
+        <v>455337219</v>
+      </c>
+      <c r="B22" t="s">
+        <v>1810</v>
+      </c>
+      <c r="C22" t="s">
+        <v>1811</v>
+      </c>
+      <c r="D22" t="s">
+        <v>1812</v>
+      </c>
+      <c r="E22" t="s">
+        <v>1813</v>
+      </c>
+      <c r="F22" t="s">
+        <v>1814</v>
+      </c>
+      <c r="G22" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H22" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I22" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J22" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K22" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L22" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M22" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N22" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O22" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P22" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q22" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R22" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S22" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T22" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U22" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A23">
+        <v>430547349</v>
+      </c>
+      <c r="B23" t="s">
+        <v>1815</v>
+      </c>
+      <c r="C23" t="s">
+        <v>1816</v>
+      </c>
+      <c r="D23" t="s">
+        <v>1817</v>
+      </c>
+      <c r="E23" t="s">
+        <v>1818</v>
+      </c>
+      <c r="F23" t="s">
+        <v>1819</v>
+      </c>
+      <c r="G23" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H23" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I23" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J23" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K23" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L23" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M23" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N23" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O23" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P23" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q23" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R23" t="s">
+        <v>111</v>
+      </c>
+      <c r="S23" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T23" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U23" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="24" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A24">
+        <v>480070438</v>
+      </c>
+      <c r="B24" t="s">
+        <v>1820</v>
+      </c>
+      <c r="C24" t="s">
+        <v>1821</v>
+      </c>
+      <c r="D24" t="s">
+        <v>1822</v>
+      </c>
+      <c r="E24" t="s">
+        <v>1823</v>
+      </c>
+      <c r="F24" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G24" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H24" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I24" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J24" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K24" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L24" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M24" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N24" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O24" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P24" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q24" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R24" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S24" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T24" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U24" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A25">
+        <v>489038359</v>
+      </c>
+      <c r="B25" t="s">
+        <v>1824</v>
+      </c>
+      <c r="C25" t="s">
+        <v>1825</v>
+      </c>
+      <c r="D25" t="s">
+        <v>1826</v>
+      </c>
+      <c r="E25" t="s">
+        <v>1827</v>
+      </c>
+      <c r="F25" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G25" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H25" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I25" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J25" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K25" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L25" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M25" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N25" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O25" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P25" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q25" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R25" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S25" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T25" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U25" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="26" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A26">
+        <v>400054484</v>
+      </c>
+      <c r="B26" t="s">
+        <v>1828</v>
+      </c>
+      <c r="C26" t="s">
+        <v>1829</v>
+      </c>
+      <c r="D26" t="s">
+        <v>1830</v>
+      </c>
+      <c r="E26" t="s">
+        <v>1831</v>
+      </c>
+      <c r="F26" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G26" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H26" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I26" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J26" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K26" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L26" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M26" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N26" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O26" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P26" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q26" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R26" t="s">
+        <v>111</v>
+      </c>
+      <c r="S26" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T26" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U26" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="27" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A27">
+        <v>490301106</v>
+      </c>
+      <c r="B27" t="s">
+        <v>1832</v>
+      </c>
+      <c r="C27" t="s">
+        <v>1833</v>
+      </c>
+      <c r="D27" t="s">
+        <v>1834</v>
+      </c>
+      <c r="E27" t="s">
+        <v>1835</v>
+      </c>
+      <c r="F27" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G27" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H27" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I27" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J27" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K27" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L27" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M27" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N27" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O27" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P27" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q27" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R27" t="s">
+        <v>111</v>
+      </c>
+      <c r="S27" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T27" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A28">
+        <v>429372360</v>
+      </c>
+      <c r="B28" t="s">
+        <v>1837</v>
+      </c>
+      <c r="C28" t="s">
+        <v>1838</v>
+      </c>
+      <c r="D28" t="s">
+        <v>1839</v>
+      </c>
+      <c r="E28" t="s">
+        <v>1840</v>
+      </c>
+      <c r="F28" t="s">
+        <v>1841</v>
+      </c>
+      <c r="G28" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H28" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I28" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J28" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K28" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L28" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M28" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N28" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O28" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P28" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q28" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R28" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S28" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T28" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U28" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A29">
+        <v>433183955</v>
+      </c>
+      <c r="B29" t="s">
+        <v>1842</v>
+      </c>
+      <c r="C29" t="s">
+        <v>1843</v>
+      </c>
+      <c r="D29" t="s">
+        <v>1844</v>
+      </c>
+      <c r="E29" t="s">
+        <v>1845</v>
+      </c>
+      <c r="F29" t="s">
+        <v>1846</v>
+      </c>
+      <c r="G29" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H29" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I29" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J29" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K29" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L29" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M29" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N29" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O29" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P29" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q29" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R29" t="s">
+        <v>111</v>
+      </c>
+      <c r="S29" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T29" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U29" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="30" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A30">
+        <v>451410126</v>
+      </c>
+      <c r="B30" t="s">
+        <v>1847</v>
+      </c>
+      <c r="C30" t="s">
+        <v>1848</v>
+      </c>
+      <c r="D30" t="s">
+        <v>1849</v>
+      </c>
+      <c r="E30" t="s">
+        <v>1850</v>
+      </c>
+      <c r="F30" t="s">
+        <v>1793</v>
+      </c>
+      <c r="G30" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H30" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I30" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J30" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K30" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L30" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M30" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N30" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O30" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P30" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q30" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R30" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S30" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T30" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U30" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="31" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A31">
+        <v>447212267</v>
+      </c>
+      <c r="B31" t="s">
+        <v>1851</v>
+      </c>
+      <c r="C31" t="s">
+        <v>1852</v>
+      </c>
+      <c r="D31" t="s">
+        <v>1853</v>
+      </c>
+      <c r="E31" t="s">
+        <v>1854</v>
+      </c>
+      <c r="F31" t="s">
+        <v>1855</v>
+      </c>
+      <c r="G31" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H31" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I31" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J31" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K31" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L31" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M31" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N31" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O31" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P31" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q31" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R31" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S31" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T31" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U31" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="32" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A32">
+        <v>462732043</v>
+      </c>
+      <c r="B32" t="s">
+        <v>1856</v>
+      </c>
+      <c r="C32" t="s">
+        <v>1857</v>
+      </c>
+      <c r="D32" t="s">
+        <v>1858</v>
+      </c>
+      <c r="E32" t="s">
+        <v>1859</v>
+      </c>
+      <c r="F32" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G32" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H32" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I32" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J32" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K32" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L32" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M32" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N32" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O32" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P32" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q32" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R32" t="s">
+        <v>111</v>
+      </c>
+      <c r="S32" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T32" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U32" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="33" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A33">
+        <v>443868501</v>
+      </c>
+      <c r="B33" t="s">
+        <v>1860</v>
+      </c>
+      <c r="C33" t="s">
+        <v>1861</v>
+      </c>
+      <c r="D33" t="s">
+        <v>1862</v>
+      </c>
+      <c r="E33" t="s">
+        <v>1863</v>
+      </c>
+      <c r="F33" t="s">
+        <v>1864</v>
+      </c>
+      <c r="G33" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H33" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I33" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J33" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K33" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L33" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M33" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N33" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O33" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P33" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q33" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R33" t="s">
+        <v>111</v>
+      </c>
+      <c r="S33" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T33" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U33" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="34" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A34">
+        <v>402735359</v>
+      </c>
+      <c r="B34" t="s">
+        <v>1866</v>
+      </c>
+      <c r="C34" t="s">
+        <v>1867</v>
+      </c>
+      <c r="D34" t="s">
+        <v>1868</v>
+      </c>
+      <c r="E34" t="s">
+        <v>1869</v>
+      </c>
+      <c r="F34" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G34" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H34" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I34" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J34" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K34" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L34" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M34" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N34" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O34" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P34" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q34" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R34" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S34" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T34" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U34" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="35" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A35">
+        <v>477669750</v>
+      </c>
+      <c r="B35" t="s">
+        <v>1871</v>
+      </c>
+      <c r="C35" t="s">
+        <v>1872</v>
+      </c>
+      <c r="D35" t="s">
+        <v>1873</v>
+      </c>
+      <c r="E35" t="s">
+        <v>1874</v>
+      </c>
+      <c r="F35" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G35" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H35" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I35" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J35" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K35" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L35" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M35" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N35" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O35" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P35" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q35" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R35" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S35" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T35" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U35" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="36" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A36">
+        <v>457495923</v>
+      </c>
+      <c r="B36" t="s">
+        <v>1876</v>
+      </c>
+      <c r="C36" t="s">
+        <v>1877</v>
+      </c>
+      <c r="D36" t="s">
+        <v>1878</v>
+      </c>
+      <c r="E36" t="s">
+        <v>1879</v>
+      </c>
+      <c r="F36" t="s">
+        <v>1740</v>
+      </c>
+      <c r="G36" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H36" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I36" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J36" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K36" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L36" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M36" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N36" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O36" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P36" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q36" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R36" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S36" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T36" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U36" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="37" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A37">
+        <v>498116677</v>
+      </c>
+      <c r="B37" t="s">
+        <v>1880</v>
+      </c>
+      <c r="C37" t="s">
+        <v>1881</v>
+      </c>
+      <c r="D37" t="s">
+        <v>1882</v>
+      </c>
+      <c r="E37" t="s">
+        <v>1883</v>
+      </c>
+      <c r="F37" t="s">
+        <v>1855</v>
+      </c>
+      <c r="G37" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H37" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I37" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J37" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K37" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L37" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M37" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N37" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O37" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P37" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q37" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R37" t="s">
+        <v>111</v>
+      </c>
+      <c r="S37" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T37" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U37" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="38" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A38">
+        <v>434675473</v>
+      </c>
+      <c r="B38" t="s">
+        <v>1884</v>
+      </c>
+      <c r="C38" t="s">
+        <v>1885</v>
+      </c>
+      <c r="D38" t="s">
+        <v>1886</v>
+      </c>
+      <c r="E38" t="s">
+        <v>1887</v>
+      </c>
+      <c r="F38" t="s">
+        <v>1888</v>
+      </c>
+      <c r="G38" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H38" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I38" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J38" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K38" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L38" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M38" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N38" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O38" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P38" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q38" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R38" t="s">
+        <v>111</v>
+      </c>
+      <c r="S38" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T38" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U38" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="39" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A39">
+        <v>439491631</v>
+      </c>
+      <c r="B39" t="s">
+        <v>1889</v>
+      </c>
+      <c r="C39" t="s">
+        <v>1890</v>
+      </c>
+      <c r="D39" t="s">
+        <v>1891</v>
+      </c>
+      <c r="E39" t="s">
+        <v>1892</v>
+      </c>
+      <c r="F39" t="s">
+        <v>1893</v>
+      </c>
+      <c r="G39" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H39" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I39" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J39" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K39" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L39" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M39" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N39" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O39" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P39" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q39" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R39" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S39" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T39" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U39" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="40" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A40">
+        <v>430942292</v>
+      </c>
+      <c r="B40" t="s">
+        <v>1894</v>
+      </c>
+      <c r="C40" t="s">
+        <v>1895</v>
+      </c>
+      <c r="D40" t="s">
+        <v>1896</v>
+      </c>
+      <c r="E40" t="s">
+        <v>1897</v>
+      </c>
+      <c r="F40" t="s">
+        <v>1898</v>
+      </c>
+      <c r="G40" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H40" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I40" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J40" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K40" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L40" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M40" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N40" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O40" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P40" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q40" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R40" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S40" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T40" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U40" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="41" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A41">
+        <v>440569669</v>
+      </c>
+      <c r="B41" t="s">
+        <v>1899</v>
+      </c>
+      <c r="C41" t="s">
+        <v>1900</v>
+      </c>
+      <c r="D41" t="s">
+        <v>1901</v>
+      </c>
+      <c r="E41" t="s">
+        <v>1902</v>
+      </c>
+      <c r="F41" t="s">
+        <v>1870</v>
+      </c>
+      <c r="G41" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H41" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I41" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J41" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K41" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L41" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M41" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N41" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O41" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P41" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q41" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R41" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S41" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T41" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U41" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="42" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A42">
+        <v>424744872</v>
+      </c>
+      <c r="B42" t="s">
+        <v>1903</v>
+      </c>
+      <c r="C42" t="s">
+        <v>1904</v>
+      </c>
+      <c r="D42" t="s">
+        <v>1905</v>
+      </c>
+      <c r="E42" t="s">
+        <v>1906</v>
+      </c>
+      <c r="F42" t="s">
+        <v>1907</v>
+      </c>
+      <c r="G42" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H42" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I42" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J42" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K42" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L42" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M42" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N42" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O42" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P42" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q42" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R42" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S42" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T42" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U42" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="43" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A43">
+        <v>460467027</v>
+      </c>
+      <c r="B43" t="s">
+        <v>1908</v>
+      </c>
+      <c r="C43" t="s">
+        <v>1909</v>
+      </c>
+      <c r="D43" t="s">
+        <v>1910</v>
+      </c>
+      <c r="E43" t="s">
+        <v>1911</v>
+      </c>
+      <c r="F43" t="s">
+        <v>1912</v>
+      </c>
+      <c r="G43" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H43" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I43" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J43" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K43" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L43" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M43" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N43" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O43" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P43" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q43" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R43" t="s">
+        <v>111</v>
+      </c>
+      <c r="S43" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T43" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U43" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="44" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A44">
+        <v>474087145</v>
+      </c>
+      <c r="B44" t="s">
+        <v>1913</v>
+      </c>
+      <c r="C44" t="s">
+        <v>1914</v>
+      </c>
+      <c r="D44" t="s">
+        <v>1915</v>
+      </c>
+      <c r="E44" t="s">
+        <v>1916</v>
+      </c>
+      <c r="F44" t="s">
+        <v>1917</v>
+      </c>
+      <c r="G44" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H44" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I44" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J44" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K44" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L44" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M44" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N44" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O44" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P44" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q44" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R44" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S44" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T44" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U44" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="45" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A45">
+        <v>488742485</v>
+      </c>
+      <c r="B45" t="s">
+        <v>1918</v>
+      </c>
+      <c r="C45" t="s">
+        <v>1919</v>
+      </c>
+      <c r="D45" t="s">
+        <v>1920</v>
+      </c>
+      <c r="E45" t="s">
+        <v>1921</v>
+      </c>
+      <c r="F45" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G45" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H45" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I45" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J45" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K45" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L45" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M45" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N45" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O45" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P45" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q45" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R45" t="s">
+        <v>111</v>
+      </c>
+      <c r="S45" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T45" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U45" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="46" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A46">
+        <v>492432795</v>
+      </c>
+      <c r="B46" t="s">
+        <v>1923</v>
+      </c>
+      <c r="C46" t="s">
+        <v>1924</v>
+      </c>
+      <c r="D46" t="s">
+        <v>1925</v>
+      </c>
+      <c r="E46" t="s">
+        <v>1926</v>
+      </c>
+      <c r="F46" t="s">
+        <v>1927</v>
+      </c>
+      <c r="G46" t="s">
+        <v>1928</v>
+      </c>
+      <c r="H46" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I46" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J46" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K46" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L46" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M46" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N46" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O46" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P46" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q46" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R46" t="s">
+        <v>111</v>
+      </c>
+      <c r="S46" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T46" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U46" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="47" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A47">
+        <v>477201917</v>
+      </c>
+      <c r="B47" t="s">
+        <v>1929</v>
+      </c>
+      <c r="C47" t="s">
+        <v>1930</v>
+      </c>
+      <c r="D47" t="s">
+        <v>1931</v>
+      </c>
+      <c r="E47" t="s">
+        <v>1932</v>
+      </c>
+      <c r="F47" t="s">
+        <v>1933</v>
+      </c>
+      <c r="G47" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H47" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I47" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J47" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K47" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L47" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M47" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N47" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O47" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P47" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q47" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R47" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S47" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T47" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U47" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="48" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A48">
+        <v>454807553</v>
+      </c>
+      <c r="B48" t="s">
+        <v>1934</v>
+      </c>
+      <c r="C48" t="s">
+        <v>1935</v>
+      </c>
+      <c r="D48" t="s">
+        <v>1936</v>
+      </c>
+      <c r="E48" t="s">
+        <v>1937</v>
+      </c>
+      <c r="F48" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G48" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H48" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I48" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J48" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K48" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L48" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M48" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N48" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O48" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P48" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q48" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R48" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S48" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T48" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U48" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="49" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A49">
+        <v>400154493</v>
+      </c>
+      <c r="B49" t="s">
+        <v>1939</v>
+      </c>
+      <c r="C49" t="s">
+        <v>1940</v>
+      </c>
+      <c r="D49" t="s">
+        <v>1941</v>
+      </c>
+      <c r="E49" t="s">
+        <v>1942</v>
+      </c>
+      <c r="F49" t="s">
+        <v>1841</v>
+      </c>
+      <c r="G49" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H49" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I49" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J49" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K49" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L49" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M49" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N49" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O49" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P49" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q49" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R49" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S49" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T49" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U49" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="50" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A50">
+        <v>465056916</v>
+      </c>
+      <c r="B50" t="s">
+        <v>1943</v>
+      </c>
+      <c r="C50" t="s">
+        <v>1944</v>
+      </c>
+      <c r="D50" t="s">
+        <v>1945</v>
+      </c>
+      <c r="E50" t="s">
+        <v>1946</v>
+      </c>
+      <c r="F50" t="s">
+        <v>1947</v>
+      </c>
+      <c r="G50" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H50" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I50" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J50" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K50" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L50" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M50" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N50" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O50" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P50" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q50" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R50" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S50" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T50" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U50" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="51" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A51">
+        <v>468299645</v>
+      </c>
+      <c r="B51" t="s">
+        <v>1948</v>
+      </c>
+      <c r="C51" t="s">
+        <v>1949</v>
+      </c>
+      <c r="D51" t="s">
+        <v>1950</v>
+      </c>
+      <c r="E51" t="s">
+        <v>1951</v>
+      </c>
+      <c r="F51" t="s">
+        <v>1952</v>
+      </c>
+      <c r="G51" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H51" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I51" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J51" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K51" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L51" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M51" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N51" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O51" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P51" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q51" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R51" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S51" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T51" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U51" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="52" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A52">
+        <v>440071487</v>
+      </c>
+      <c r="B52" t="s">
+        <v>1953</v>
+      </c>
+      <c r="C52" t="s">
+        <v>1954</v>
+      </c>
+      <c r="D52" t="s">
+        <v>1955</v>
+      </c>
+      <c r="E52" t="s">
+        <v>1956</v>
+      </c>
+      <c r="F52" t="s">
+        <v>1957</v>
+      </c>
+      <c r="G52" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H52" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I52" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J52" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K52" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L52" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M52" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N52" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O52" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P52" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q52" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R52" t="s">
+        <v>111</v>
+      </c>
+      <c r="S52" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T52" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U52" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="53" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A53">
+        <v>405858241</v>
+      </c>
+      <c r="B53" t="s">
+        <v>1958</v>
+      </c>
+      <c r="C53" t="s">
+        <v>1959</v>
+      </c>
+      <c r="D53" t="s">
+        <v>1960</v>
+      </c>
+      <c r="E53" t="s">
+        <v>1961</v>
+      </c>
+      <c r="F53" t="s">
+        <v>1962</v>
+      </c>
+      <c r="G53" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H53" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I53" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J53" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K53" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L53" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M53" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N53" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O53" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P53" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q53" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R53" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S53" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T53" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U53" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="54" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A54">
+        <v>455026398</v>
+      </c>
+      <c r="B54" t="s">
+        <v>1963</v>
+      </c>
+      <c r="C54" t="s">
+        <v>1964</v>
+      </c>
+      <c r="D54" t="s">
+        <v>1965</v>
+      </c>
+      <c r="E54" t="s">
+        <v>1966</v>
+      </c>
+      <c r="F54" t="s">
+        <v>1967</v>
+      </c>
+      <c r="G54" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H54" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I54" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J54" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K54" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L54" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M54" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N54" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O54" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P54" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q54" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R54" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S54" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T54" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U54" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="55" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A55">
+        <v>438571356</v>
+      </c>
+      <c r="B55" t="s">
+        <v>1968</v>
+      </c>
+      <c r="C55" t="s">
+        <v>1969</v>
+      </c>
+      <c r="D55" t="s">
+        <v>1970</v>
+      </c>
+      <c r="E55" t="s">
+        <v>1971</v>
+      </c>
+      <c r="F55" t="s">
+        <v>1766</v>
+      </c>
+      <c r="G55" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H55" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I55" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J55" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K55" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L55" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M55" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N55" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O55" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P55" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q55" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R55" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S55" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T55" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U55" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="56" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A56">
+        <v>419538047</v>
+      </c>
+      <c r="B56" t="s">
+        <v>1972</v>
+      </c>
+      <c r="C56" t="s">
+        <v>1973</v>
+      </c>
+      <c r="D56" t="s">
+        <v>1974</v>
+      </c>
+      <c r="E56" t="s">
+        <v>1975</v>
+      </c>
+      <c r="F56" t="s">
+        <v>1976</v>
+      </c>
+      <c r="G56" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H56" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I56" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J56" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K56" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L56" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M56" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N56" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O56" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P56" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q56" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R56" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S56" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T56" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U56" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="57" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A57">
+        <v>461682508</v>
+      </c>
+      <c r="B57" t="s">
+        <v>1977</v>
+      </c>
+      <c r="C57" t="s">
+        <v>1978</v>
+      </c>
+      <c r="D57" t="s">
+        <v>1979</v>
+      </c>
+      <c r="E57" t="s">
+        <v>1980</v>
+      </c>
+      <c r="F57" t="s">
+        <v>1981</v>
+      </c>
+      <c r="G57" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H57" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I57" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J57" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K57" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L57" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M57" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N57" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O57" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P57" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q57" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R57" t="s">
+        <v>111</v>
+      </c>
+      <c r="S57" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T57" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U57" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="58" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A58">
+        <v>464855088</v>
+      </c>
+      <c r="B58" t="s">
+        <v>1982</v>
+      </c>
+      <c r="C58" t="s">
+        <v>1983</v>
+      </c>
+      <c r="D58" t="s">
+        <v>1984</v>
+      </c>
+      <c r="E58" t="s">
+        <v>1985</v>
+      </c>
+      <c r="F58" t="s">
+        <v>1875</v>
+      </c>
+      <c r="G58" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H58" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I58" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J58" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K58" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L58" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M58" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N58" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O58" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P58" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q58" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R58" t="s">
+        <v>111</v>
+      </c>
+      <c r="S58" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T58" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U58" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="59" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A59">
+        <v>447287718</v>
+      </c>
+      <c r="B59" t="s">
+        <v>1986</v>
+      </c>
+      <c r="C59" t="s">
+        <v>1987</v>
+      </c>
+      <c r="D59" t="s">
+        <v>1988</v>
+      </c>
+      <c r="E59" t="s">
+        <v>1989</v>
+      </c>
+      <c r="F59" t="s">
+        <v>1990</v>
+      </c>
+      <c r="G59" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H59" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I59" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J59" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K59" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L59" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M59" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N59" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O59" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P59" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q59" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R59" t="s">
+        <v>111</v>
+      </c>
+      <c r="S59" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T59" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U59" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="60" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A60">
+        <v>443851498</v>
+      </c>
+      <c r="B60" t="s">
+        <v>1991</v>
+      </c>
+      <c r="C60" t="s">
+        <v>1992</v>
+      </c>
+      <c r="D60" t="s">
+        <v>1993</v>
+      </c>
+      <c r="E60" t="s">
+        <v>1994</v>
+      </c>
+      <c r="F60" t="s">
+        <v>1995</v>
+      </c>
+      <c r="G60" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H60" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I60" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J60" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K60" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L60" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M60" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N60" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O60" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P60" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q60" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R60" t="s">
+        <v>111</v>
+      </c>
+      <c r="S60" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T60" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U60" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="61" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A61">
+        <v>497202721</v>
+      </c>
+      <c r="B61" t="s">
+        <v>1996</v>
+      </c>
+      <c r="C61" t="s">
+        <v>1997</v>
+      </c>
+      <c r="D61" t="s">
+        <v>1998</v>
+      </c>
+      <c r="E61" t="s">
+        <v>1999</v>
+      </c>
+      <c r="F61" t="s">
+        <v>2000</v>
+      </c>
+      <c r="G61" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H61" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I61" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J61" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K61" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L61" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M61" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N61" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O61" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P61" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q61" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R61" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S61" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T61" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U61" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="62" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A62">
+        <v>414541967</v>
+      </c>
+      <c r="B62" t="s">
+        <v>2001</v>
+      </c>
+      <c r="C62" t="s">
+        <v>2002</v>
+      </c>
+      <c r="D62" t="s">
+        <v>2003</v>
+      </c>
+      <c r="E62" t="s">
+        <v>2004</v>
+      </c>
+      <c r="F62" t="s">
+        <v>1836</v>
+      </c>
+      <c r="G62" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H62" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I62" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J62" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K62" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L62" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M62" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N62" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O62" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P62" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q62" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R62" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S62" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T62" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U62" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="63" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A63">
+        <v>415585427</v>
+      </c>
+      <c r="B63" t="s">
+        <v>2005</v>
+      </c>
+      <c r="C63" t="s">
+        <v>2006</v>
+      </c>
+      <c r="D63" t="s">
+        <v>2007</v>
+      </c>
+      <c r="E63" t="s">
+        <v>2008</v>
+      </c>
+      <c r="F63" t="s">
+        <v>2009</v>
+      </c>
+      <c r="G63" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H63" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I63" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J63" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K63" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L63" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M63" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N63" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O63" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P63" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q63" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R63" t="s">
+        <v>111</v>
+      </c>
+      <c r="S63" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T63" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U63" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="64" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A64">
+        <v>449731689</v>
+      </c>
+      <c r="B64" t="s">
+        <v>2010</v>
+      </c>
+      <c r="C64" t="s">
+        <v>2011</v>
+      </c>
+      <c r="D64" t="s">
+        <v>2012</v>
+      </c>
+      <c r="E64" t="s">
+        <v>2013</v>
+      </c>
+      <c r="F64" t="s">
+        <v>2014</v>
+      </c>
+      <c r="G64" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H64" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I64" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J64" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K64" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L64" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M64" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N64" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O64" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P64" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q64" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R64" t="s">
+        <v>111</v>
+      </c>
+      <c r="S64" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T64" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U64" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="65" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A65">
+        <v>432691263</v>
+      </c>
+      <c r="B65" t="s">
+        <v>2015</v>
+      </c>
+      <c r="C65" t="s">
+        <v>2016</v>
+      </c>
+      <c r="D65" t="s">
+        <v>2017</v>
+      </c>
+      <c r="E65" t="s">
+        <v>2018</v>
+      </c>
+      <c r="F65" t="s">
+        <v>2019</v>
+      </c>
+      <c r="G65" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H65" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I65" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J65" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K65" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L65" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M65" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N65" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O65" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P65" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q65" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R65" t="s">
+        <v>111</v>
+      </c>
+      <c r="S65" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T65" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U65" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="66" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A66">
+        <v>403460153</v>
+      </c>
+      <c r="B66" t="s">
+        <v>2020</v>
+      </c>
+      <c r="C66" t="s">
+        <v>2021</v>
+      </c>
+      <c r="D66" t="s">
+        <v>2022</v>
+      </c>
+      <c r="E66" t="s">
+        <v>2023</v>
+      </c>
+      <c r="F66" t="s">
+        <v>2024</v>
+      </c>
+      <c r="G66" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H66" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I66" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J66" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K66" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L66" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M66" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N66" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O66" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P66" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q66" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R66" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S66" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T66" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U66" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="67" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A67">
+        <v>479680504</v>
+      </c>
+      <c r="B67" t="s">
+        <v>2025</v>
+      </c>
+      <c r="C67" t="s">
+        <v>2026</v>
+      </c>
+      <c r="D67" t="s">
+        <v>2027</v>
+      </c>
+      <c r="E67" t="s">
+        <v>2028</v>
+      </c>
+      <c r="F67" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G67" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H67" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I67" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J67" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K67" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L67" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M67" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N67" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O67" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P67" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q67" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R67" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S67" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T67" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U67" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="68" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A68">
+        <v>409863756</v>
+      </c>
+      <c r="B68" t="s">
+        <v>2029</v>
+      </c>
+      <c r="C68" t="s">
+        <v>2030</v>
+      </c>
+      <c r="D68" t="s">
+        <v>2031</v>
+      </c>
+      <c r="E68" t="s">
+        <v>2032</v>
+      </c>
+      <c r="F68" t="s">
+        <v>2033</v>
+      </c>
+      <c r="G68" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H68" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I68" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J68" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K68" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L68" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M68" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N68" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O68" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P68" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q68" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R68" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S68" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T68" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U68" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="69" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A69">
+        <v>430667888</v>
+      </c>
+      <c r="B69" t="s">
+        <v>2034</v>
+      </c>
+      <c r="C69" t="s">
+        <v>2035</v>
+      </c>
+      <c r="D69" t="s">
+        <v>2036</v>
+      </c>
+      <c r="E69" t="s">
+        <v>2037</v>
+      </c>
+      <c r="F69" t="s">
+        <v>2038</v>
+      </c>
+      <c r="G69" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H69" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I69" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J69" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K69" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L69" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M69" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N69" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O69" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P69" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q69" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R69" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S69" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T69" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U69" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="70" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A70">
+        <v>499937039</v>
+      </c>
+      <c r="B70" t="s">
+        <v>2039</v>
+      </c>
+      <c r="C70" t="s">
+        <v>2040</v>
+      </c>
+      <c r="D70" t="s">
+        <v>2041</v>
+      </c>
+      <c r="E70" t="s">
+        <v>2042</v>
+      </c>
+      <c r="F70" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G70" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H70" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I70" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J70" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K70" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L70" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M70" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N70" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O70" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P70" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q70" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R70" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S70" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T70" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U70" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="71" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A71">
+        <v>428553319</v>
+      </c>
+      <c r="B71" t="s">
+        <v>2044</v>
+      </c>
+      <c r="C71" t="s">
+        <v>2045</v>
+      </c>
+      <c r="D71" t="s">
+        <v>2046</v>
+      </c>
+      <c r="E71" t="s">
+        <v>2047</v>
+      </c>
+      <c r="F71" t="s">
+        <v>1660</v>
+      </c>
+      <c r="G71" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H71" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I71" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J71" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K71" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L71" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M71" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N71" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O71" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P71" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q71" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R71" t="s">
+        <v>111</v>
+      </c>
+      <c r="S71" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T71" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U71" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="72" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A72">
+        <v>494314632</v>
+      </c>
+      <c r="B72" t="s">
+        <v>2048</v>
+      </c>
+      <c r="C72" t="s">
+        <v>2049</v>
+      </c>
+      <c r="D72" t="s">
+        <v>2050</v>
+      </c>
+      <c r="E72" t="s">
+        <v>2051</v>
+      </c>
+      <c r="F72" t="s">
+        <v>1804</v>
+      </c>
+      <c r="G72" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H72" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I72" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J72" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K72" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L72" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M72" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N72" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O72" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P72" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q72" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R72" t="s">
+        <v>111</v>
+      </c>
+      <c r="S72" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T72" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U72" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="73" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A73">
+        <v>441827259</v>
+      </c>
+      <c r="B73" t="s">
+        <v>2052</v>
+      </c>
+      <c r="C73" t="s">
+        <v>2053</v>
+      </c>
+      <c r="D73" t="s">
+        <v>2054</v>
+      </c>
+      <c r="E73" t="s">
+        <v>2055</v>
+      </c>
+      <c r="F73" t="s">
+        <v>1734</v>
+      </c>
+      <c r="G73" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H73" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I73" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J73" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K73" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L73" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M73" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N73" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O73" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P73" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q73" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R73" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S73" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T73" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U73" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="74" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A74">
+        <v>428933176</v>
+      </c>
+      <c r="B74" t="s">
+        <v>2056</v>
+      </c>
+      <c r="C74" t="s">
+        <v>2057</v>
+      </c>
+      <c r="D74" t="s">
+        <v>2058</v>
+      </c>
+      <c r="E74" t="s">
+        <v>2059</v>
+      </c>
+      <c r="F74" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G74" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H74" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I74" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J74" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K74" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L74" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M74" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N74" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O74" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P74" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q74" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R74" t="s">
+        <v>111</v>
+      </c>
+      <c r="S74" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T74" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U74" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="75" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A75">
+        <v>428351344</v>
+      </c>
+      <c r="B75" t="s">
+        <v>2061</v>
+      </c>
+      <c r="C75" t="s">
+        <v>2062</v>
+      </c>
+      <c r="D75" t="s">
+        <v>2063</v>
+      </c>
+      <c r="E75" t="s">
+        <v>2064</v>
+      </c>
+      <c r="F75" t="s">
+        <v>2065</v>
+      </c>
+      <c r="G75" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H75" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I75" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J75" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K75" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L75" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M75" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N75" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O75" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P75" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q75" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R75" t="s">
+        <v>111</v>
+      </c>
+      <c r="S75" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T75" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U75" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="76" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A76">
+        <v>410450542</v>
+      </c>
+      <c r="B76" t="s">
+        <v>2066</v>
+      </c>
+      <c r="C76" t="s">
+        <v>2067</v>
+      </c>
+      <c r="D76" t="s">
+        <v>2068</v>
+      </c>
+      <c r="E76" t="s">
+        <v>2069</v>
+      </c>
+      <c r="F76" t="s">
+        <v>1922</v>
+      </c>
+      <c r="G76" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H76" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I76" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J76" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K76" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L76" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M76" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N76" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O76" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P76" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q76" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R76" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S76" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T76" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U76" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="77" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A77">
+        <v>432657384</v>
+      </c>
+      <c r="B77" t="s">
+        <v>2070</v>
+      </c>
+      <c r="C77" t="s">
+        <v>2071</v>
+      </c>
+      <c r="D77" t="s">
+        <v>2072</v>
+      </c>
+      <c r="E77" t="s">
+        <v>2073</v>
+      </c>
+      <c r="F77" t="s">
+        <v>2074</v>
+      </c>
+      <c r="G77" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H77" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I77" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J77" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K77" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L77" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M77" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N77" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O77" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P77" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q77" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R77" t="s">
+        <v>111</v>
+      </c>
+      <c r="S77" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T77" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U77" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="78" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A78">
+        <v>434355473</v>
+      </c>
+      <c r="B78" t="s">
+        <v>2075</v>
+      </c>
+      <c r="C78" t="s">
+        <v>2076</v>
+      </c>
+      <c r="D78" t="s">
+        <v>2077</v>
+      </c>
+      <c r="E78" t="s">
+        <v>2078</v>
+      </c>
+      <c r="F78" t="s">
+        <v>2079</v>
+      </c>
+      <c r="G78" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H78" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I78" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J78" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K78" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L78" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M78" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N78" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O78" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P78" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q78" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R78" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S78" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T78" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U78" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="79" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A79">
+        <v>440643870</v>
+      </c>
+      <c r="B79" t="s">
+        <v>2080</v>
+      </c>
+      <c r="C79" t="s">
+        <v>2081</v>
+      </c>
+      <c r="D79" t="s">
+        <v>2082</v>
+      </c>
+      <c r="E79" t="s">
+        <v>2083</v>
+      </c>
+      <c r="F79" t="s">
+        <v>2043</v>
+      </c>
+      <c r="G79" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H79" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I79" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J79" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K79" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L79" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M79" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N79" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O79" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P79" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q79" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R79" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S79" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T79" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U79" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="80" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A80">
+        <v>474399083</v>
+      </c>
+      <c r="B80" t="s">
+        <v>2084</v>
+      </c>
+      <c r="C80" t="s">
+        <v>2085</v>
+      </c>
+      <c r="D80" t="s">
+        <v>2086</v>
+      </c>
+      <c r="E80" t="s">
+        <v>2087</v>
+      </c>
+      <c r="F80" t="s">
+        <v>2088</v>
+      </c>
+      <c r="G80" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H80" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I80" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J80" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K80" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L80" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M80" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N80" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O80" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P80" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q80" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R80" t="s">
+        <v>111</v>
+      </c>
+      <c r="S80" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T80" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U80" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="81" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A81">
+        <v>494975377</v>
+      </c>
+      <c r="B81" t="s">
+        <v>2089</v>
+      </c>
+      <c r="C81" t="s">
+        <v>2090</v>
+      </c>
+      <c r="D81" t="s">
+        <v>2091</v>
+      </c>
+      <c r="E81" t="s">
+        <v>2092</v>
+      </c>
+      <c r="F81" t="s">
+        <v>2074</v>
+      </c>
+      <c r="G81" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H81" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I81" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J81" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K81" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L81" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M81" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N81" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O81" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P81" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q81" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R81" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S81" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T81" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U81" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="82" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A82">
+        <v>474888554</v>
+      </c>
+      <c r="B82" t="s">
+        <v>2093</v>
+      </c>
+      <c r="C82" t="s">
+        <v>2094</v>
+      </c>
+      <c r="D82" t="s">
+        <v>2095</v>
+      </c>
+      <c r="E82" t="s">
+        <v>2096</v>
+      </c>
+      <c r="F82" t="s">
+        <v>2097</v>
+      </c>
+      <c r="G82" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H82" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I82" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J82" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K82" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L82" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M82" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N82" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O82" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P82" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q82" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R82" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S82" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T82" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U82" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="83" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A83">
+        <v>411370793</v>
+      </c>
+      <c r="B83" t="s">
+        <v>2098</v>
+      </c>
+      <c r="C83" t="s">
+        <v>2099</v>
+      </c>
+      <c r="D83" t="s">
+        <v>2100</v>
+      </c>
+      <c r="E83" t="s">
+        <v>2101</v>
+      </c>
+      <c r="F83" t="s">
+        <v>2102</v>
+      </c>
+      <c r="G83" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H83" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I83" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J83" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K83" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L83" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M83" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N83" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O83" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P83" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q83" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R83" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S83" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T83" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U83" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="84" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A84">
+        <v>425770506</v>
+      </c>
+      <c r="B84" t="s">
+        <v>2103</v>
+      </c>
+      <c r="C84" t="s">
+        <v>2104</v>
+      </c>
+      <c r="D84" t="s">
+        <v>2105</v>
+      </c>
+      <c r="E84" t="s">
+        <v>2106</v>
+      </c>
+      <c r="F84" t="s">
+        <v>2079</v>
+      </c>
+      <c r="G84" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H84" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I84" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J84" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K84" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L84" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M84" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N84" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O84" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P84" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q84" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R84" t="s">
+        <v>111</v>
+      </c>
+      <c r="S84" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T84" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U84" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="85" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A85">
+        <v>448895439</v>
+      </c>
+      <c r="B85" t="s">
+        <v>2107</v>
+      </c>
+      <c r="C85" t="s">
+        <v>2108</v>
+      </c>
+      <c r="D85" t="s">
+        <v>2109</v>
+      </c>
+      <c r="E85" t="s">
+        <v>2110</v>
+      </c>
+      <c r="F85" t="s">
+        <v>2111</v>
+      </c>
+      <c r="G85" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H85" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I85" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J85" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K85" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L85" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M85" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N85" t="s">
+        <v>1712</v>
+      </c>
+      <c r="O85" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P85" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q85" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R85" t="s">
+        <v>111</v>
+      </c>
+      <c r="S85" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T85" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U85" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="86" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A86">
+        <v>481156554</v>
+      </c>
+      <c r="B86" t="s">
+        <v>2112</v>
+      </c>
+      <c r="C86" t="s">
+        <v>2113</v>
+      </c>
+      <c r="D86" t="s">
+        <v>2114</v>
+      </c>
+      <c r="E86" t="s">
+        <v>2115</v>
+      </c>
+      <c r="F86" t="s">
+        <v>2116</v>
+      </c>
+      <c r="G86" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H86" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I86" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J86" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K86" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L86" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M86" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N86" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O86" t="s">
+        <v>1735</v>
+      </c>
+      <c r="P86" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q86" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R86" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S86" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T86" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U86" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="87" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A87">
+        <v>429801436</v>
+      </c>
+      <c r="B87" t="s">
+        <v>2117</v>
+      </c>
+      <c r="C87" t="s">
+        <v>2118</v>
+      </c>
+      <c r="D87" t="s">
+        <v>2119</v>
+      </c>
+      <c r="E87" t="s">
+        <v>2120</v>
+      </c>
+      <c r="F87" t="s">
+        <v>2116</v>
+      </c>
+      <c r="G87" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H87" t="s">
+        <v>1679</v>
+      </c>
+      <c r="I87" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J87" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K87" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L87" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M87" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N87" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O87" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P87" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q87" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R87" t="s">
+        <v>111</v>
+      </c>
+      <c r="S87" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T87" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U87" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="88" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A88">
+        <v>438504300</v>
+      </c>
+      <c r="B88" t="s">
+        <v>2121</v>
+      </c>
+      <c r="C88" t="s">
+        <v>2122</v>
+      </c>
+      <c r="D88" t="s">
+        <v>2123</v>
+      </c>
+      <c r="E88" t="s">
+        <v>2124</v>
+      </c>
+      <c r="F88" t="s">
+        <v>2125</v>
+      </c>
+      <c r="G88" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H88" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I88" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J88" t="s">
+        <v>1720</v>
+      </c>
+      <c r="K88" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L88" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M88" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N88" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O88" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P88" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q88" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R88" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S88" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T88" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U88" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="89" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A89">
+        <v>440419829</v>
+      </c>
+      <c r="B89" t="s">
+        <v>2126</v>
+      </c>
+      <c r="C89" t="s">
+        <v>2127</v>
+      </c>
+      <c r="D89" t="s">
+        <v>2128</v>
+      </c>
+      <c r="E89" t="s">
+        <v>2129</v>
+      </c>
+      <c r="F89" t="s">
+        <v>2038</v>
+      </c>
+      <c r="G89" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H89" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I89" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J89" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K89" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L89" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M89" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N89" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O89" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P89" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q89" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R89" t="s">
+        <v>111</v>
+      </c>
+      <c r="S89" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T89" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U89" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="90" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A90">
+        <v>455910756</v>
+      </c>
+      <c r="B90" t="s">
+        <v>2130</v>
+      </c>
+      <c r="C90" t="s">
+        <v>2131</v>
+      </c>
+      <c r="D90" t="s">
+        <v>2132</v>
+      </c>
+      <c r="E90" t="s">
+        <v>2133</v>
+      </c>
+      <c r="F90" t="s">
+        <v>1746</v>
+      </c>
+      <c r="G90" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H90" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I90" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J90" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K90" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L90" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M90" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N90" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O90" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P90" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q90" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R90" t="s">
+        <v>111</v>
+      </c>
+      <c r="S90" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T90" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U90" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="91" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A91">
+        <v>432363373</v>
+      </c>
+      <c r="B91" t="s">
+        <v>2134</v>
+      </c>
+      <c r="C91" t="s">
+        <v>2135</v>
+      </c>
+      <c r="D91" t="s">
+        <v>2136</v>
+      </c>
+      <c r="E91" t="s">
+        <v>2137</v>
+      </c>
+      <c r="F91" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G91" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H91" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I91" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J91" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K91" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L91" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M91" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N91" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O91" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P91" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q91" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R91" t="s">
+        <v>111</v>
+      </c>
+      <c r="S91" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T91" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U91" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="92" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A92">
+        <v>461428713</v>
+      </c>
+      <c r="B92" t="s">
+        <v>2138</v>
+      </c>
+      <c r="C92" t="s">
+        <v>2139</v>
+      </c>
+      <c r="D92" t="s">
+        <v>2140</v>
+      </c>
+      <c r="E92" t="s">
+        <v>2141</v>
+      </c>
+      <c r="F92" t="s">
+        <v>1809</v>
+      </c>
+      <c r="G92" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H92" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I92" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J92" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K92" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L92" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M92" t="s">
+        <v>1666</v>
+      </c>
+      <c r="N92" t="s">
+        <v>1698</v>
+      </c>
+      <c r="O92" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P92" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q92" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R92" t="s">
+        <v>111</v>
+      </c>
+      <c r="S92" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T92" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U92" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="93" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A93">
+        <v>444550177</v>
+      </c>
+      <c r="B93" t="s">
+        <v>2142</v>
+      </c>
+      <c r="C93" t="s">
+        <v>2143</v>
+      </c>
+      <c r="D93" t="s">
+        <v>2144</v>
+      </c>
+      <c r="E93" t="s">
+        <v>2145</v>
+      </c>
+      <c r="F93" t="s">
+        <v>2146</v>
+      </c>
+      <c r="G93" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H93" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I93" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J93" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K93" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L93" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M93" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N93" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O93" t="s">
+        <v>1698</v>
+      </c>
+      <c r="P93" t="s">
+        <v>1684</v>
+      </c>
+      <c r="Q93" t="s">
+        <v>1685</v>
+      </c>
+      <c r="R93" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S93" t="s">
+        <v>1701</v>
+      </c>
+      <c r="T93" t="s">
+        <v>1702</v>
+      </c>
+      <c r="U93" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="94" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A94">
+        <v>424220459</v>
+      </c>
+      <c r="B94" t="s">
+        <v>2147</v>
+      </c>
+      <c r="C94" t="s">
+        <v>2148</v>
+      </c>
+      <c r="D94" t="s">
+        <v>2149</v>
+      </c>
+      <c r="E94" t="s">
+        <v>2150</v>
+      </c>
+      <c r="F94" t="s">
+        <v>1938</v>
+      </c>
+      <c r="G94" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H94" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I94" t="s">
+        <v>1779</v>
+      </c>
+      <c r="J94" t="s">
+        <v>1865</v>
+      </c>
+      <c r="K94" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L94" t="s">
+        <v>1689</v>
+      </c>
+      <c r="M94" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N94" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O94" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P94" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q94" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R94" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S94" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T94" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U94" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="95" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A95">
+        <v>436850196</v>
+      </c>
+      <c r="B95" t="s">
+        <v>2151</v>
+      </c>
+      <c r="C95" t="s">
+        <v>2152</v>
+      </c>
+      <c r="D95" t="s">
+        <v>2153</v>
+      </c>
+      <c r="E95" t="s">
+        <v>2154</v>
+      </c>
+      <c r="F95" t="s">
+        <v>2155</v>
+      </c>
+      <c r="G95" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H95" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I95" t="s">
+        <v>1756</v>
+      </c>
+      <c r="J95" t="s">
+        <v>1728</v>
+      </c>
+      <c r="K95" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L95" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M95" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N95" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O95" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P95" t="s">
+        <v>1794</v>
+      </c>
+      <c r="Q95" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R95" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S95" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T95" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U95" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="96" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A96">
+        <v>404346684</v>
+      </c>
+      <c r="B96" t="s">
+        <v>2156</v>
+      </c>
+      <c r="C96" t="s">
+        <v>2157</v>
+      </c>
+      <c r="D96" t="s">
+        <v>2158</v>
+      </c>
+      <c r="E96" t="s">
+        <v>2159</v>
+      </c>
+      <c r="F96" t="s">
+        <v>1678</v>
+      </c>
+      <c r="G96" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H96" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I96" t="s">
+        <v>1662</v>
+      </c>
+      <c r="J96" t="s">
+        <v>1681</v>
+      </c>
+      <c r="K96" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L96" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M96" t="s">
+        <v>1690</v>
+      </c>
+      <c r="N96" t="s">
+        <v>1667</v>
+      </c>
+      <c r="O96" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P96" t="s">
+        <v>1668</v>
+      </c>
+      <c r="Q96" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R96" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S96" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T96" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U96" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="97" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A97">
+        <v>451940566</v>
+      </c>
+      <c r="B97" t="s">
+        <v>2160</v>
+      </c>
+      <c r="C97" t="s">
+        <v>2161</v>
+      </c>
+      <c r="D97" t="s">
+        <v>2162</v>
+      </c>
+      <c r="E97" t="s">
+        <v>2163</v>
+      </c>
+      <c r="F97" t="s">
+        <v>1799</v>
+      </c>
+      <c r="G97" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H97" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I97" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J97" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K97" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L97" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M97" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N97" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O97" t="s">
+        <v>1712</v>
+      </c>
+      <c r="P97" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q97" t="s">
+        <v>1722</v>
+      </c>
+      <c r="R97" t="s">
+        <v>111</v>
+      </c>
+      <c r="S97" t="s">
+        <v>1687</v>
+      </c>
+      <c r="T97" t="s">
+        <v>1688</v>
+      </c>
+      <c r="U97" t="s">
+        <v>1673</v>
+      </c>
+    </row>
+    <row r="98" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A98">
+        <v>442894344</v>
+      </c>
+      <c r="B98" t="s">
+        <v>2164</v>
+      </c>
+      <c r="C98" t="s">
+        <v>2165</v>
+      </c>
+      <c r="D98" t="s">
+        <v>2166</v>
+      </c>
+      <c r="E98" t="s">
+        <v>2167</v>
+      </c>
+      <c r="F98" t="s">
+        <v>1761</v>
+      </c>
+      <c r="G98" t="s">
+        <v>1618</v>
+      </c>
+      <c r="H98" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I98" t="s">
+        <v>1710</v>
+      </c>
+      <c r="J98" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K98" t="s">
+        <v>1682</v>
+      </c>
+      <c r="L98" t="s">
+        <v>1721</v>
+      </c>
+      <c r="M98" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N98" t="s">
+        <v>1683</v>
+      </c>
+      <c r="O98" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P98" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q98" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R98" t="s">
+        <v>1686</v>
+      </c>
+      <c r="S98" t="s">
+        <v>1713</v>
+      </c>
+      <c r="T98" t="s">
+        <v>1714</v>
+      </c>
+      <c r="U98" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="99" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A99">
+        <v>448438711</v>
+      </c>
+      <c r="B99" t="s">
+        <v>2168</v>
+      </c>
+      <c r="C99" t="s">
+        <v>2169</v>
+      </c>
+      <c r="D99" t="s">
+        <v>2170</v>
+      </c>
+      <c r="E99" t="s">
+        <v>2171</v>
+      </c>
+      <c r="F99" t="s">
+        <v>1841</v>
+      </c>
+      <c r="G99" t="s">
+        <v>1622</v>
+      </c>
+      <c r="H99" t="s">
+        <v>1661</v>
+      </c>
+      <c r="I99" t="s">
+        <v>1680</v>
+      </c>
+      <c r="J99" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K99" t="s">
+        <v>1747</v>
+      </c>
+      <c r="L99" t="s">
+        <v>1729</v>
+      </c>
+      <c r="M99" t="s">
+        <v>1767</v>
+      </c>
+      <c r="N99" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O99" t="s">
+        <v>1683</v>
+      </c>
+      <c r="P99" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q99" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R99" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S99" t="s">
+        <v>1749</v>
+      </c>
+      <c r="T99" t="s">
+        <v>1750</v>
+      </c>
+      <c r="U99" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="100" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A100">
+        <v>460394554</v>
+      </c>
+      <c r="B100" t="s">
+        <v>2172</v>
+      </c>
+      <c r="C100" t="s">
+        <v>2173</v>
+      </c>
+      <c r="D100" t="s">
+        <v>2174</v>
+      </c>
+      <c r="E100" t="s">
+        <v>2175</v>
+      </c>
+      <c r="F100" t="s">
+        <v>2060</v>
+      </c>
+      <c r="G100" t="s">
+        <v>1620</v>
+      </c>
+      <c r="H100" t="s">
+        <v>1709</v>
+      </c>
+      <c r="I100" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J100" t="s">
+        <v>1663</v>
+      </c>
+      <c r="K100" t="s">
+        <v>1664</v>
+      </c>
+      <c r="L100" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M100" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N100" t="s">
+        <v>1735</v>
+      </c>
+      <c r="O100" t="s">
+        <v>1667</v>
+      </c>
+      <c r="P100" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q100" t="s">
+        <v>1700</v>
+      </c>
+      <c r="R100" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S100" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T100" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U100" t="s">
+        <v>1703</v>
+      </c>
+    </row>
+    <row r="101" spans="1:21" x14ac:dyDescent="0.3">
+      <c r="A101">
+        <v>446442431</v>
+      </c>
+      <c r="B101" t="s">
+        <v>2176</v>
+      </c>
+      <c r="C101" t="s">
+        <v>2177</v>
+      </c>
+      <c r="D101" t="s">
+        <v>2178</v>
+      </c>
+      <c r="E101" t="s">
+        <v>2179</v>
+      </c>
+      <c r="F101" t="s">
+        <v>2000</v>
+      </c>
+      <c r="G101" t="s">
+        <v>1696</v>
+      </c>
+      <c r="H101" t="s">
+        <v>1778</v>
+      </c>
+      <c r="I101" t="s">
+        <v>1741</v>
+      </c>
+      <c r="J101" t="s">
+        <v>1664</v>
+      </c>
+      <c r="K101" t="s">
+        <v>1697</v>
+      </c>
+      <c r="L101" t="s">
+        <v>1665</v>
+      </c>
+      <c r="M101" t="s">
+        <v>1711</v>
+      </c>
+      <c r="N101" t="s">
+        <v>1748</v>
+      </c>
+      <c r="O101" t="s">
+        <v>1748</v>
+      </c>
+      <c r="P101" t="s">
+        <v>1699</v>
+      </c>
+      <c r="Q101" t="s">
+        <v>1669</v>
+      </c>
+      <c r="R101" t="s">
+        <v>1670</v>
+      </c>
+      <c r="S101" t="s">
+        <v>1671</v>
+      </c>
+      <c r="T101" t="s">
+        <v>1672</v>
+      </c>
+      <c r="U101" t="s">
+        <v>1673</v>
       </c>
     </row>
   </sheetData>
